--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7341,10 +7341,10 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7538,10 +7538,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7341,10 +7341,10 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7538,10 +7538,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>6.38</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G36" t="n">

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G36" t="n">

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7144,10 +7144,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7341,10 +7341,10 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G36" t="n">

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI37"/>
+  <dimension ref="A1:BI35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.13</v>
+        <v>3.34</v>
       </c>
       <c r="R21" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="R22" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6264,27 +6264,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>46132.79166666666</v>
+        <v>46132.83333333334</v>
       </c>
     </row>
     <row r="31">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46132.83333333334</v>
+        <v>46132.875</v>
       </c>
     </row>
     <row r="34">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7438,400 +7438,6 @@
       </c>
       <c r="BI35" s="3" t="n">
         <v>46132.875</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>46132</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Puerto Montt</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Deportes Temuco</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI36" s="3" t="n">
-        <v>46132.875</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>46132</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Cavalier</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Spanish Town Police FC</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI37" s="3" t="n">
-        <v>46132.89583333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G35" t="n">

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="R21" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.13</v>
+        <v>3.34</v>
       </c>
       <c r="R22" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.69</v>
+        <v>1.82</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="R27" t="n">
-        <v>2.16</v>
+        <v>4.22</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7144,10 +7144,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7341,10 +7341,10 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="R11" t="n">
-        <v>2.99</v>
+        <v>3.41</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.13</v>
+        <v>3.34</v>
       </c>
       <c r="R21" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="R22" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7144,10 +7144,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7341,10 +7341,10 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.72</v>
+        <v>3.62</v>
       </c>
       <c r="R11" t="n">
-        <v>3.41</v>
+        <v>2.99</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="R12" t="n">
-        <v>2.99</v>
+        <v>3.41</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="R21" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.13</v>
+        <v>3.34</v>
       </c>
       <c r="R22" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="R11" t="n">
-        <v>2.99</v>
+        <v>3.41</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.13</v>
+        <v>3.34</v>
       </c>
       <c r="R21" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="R22" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.69</v>
+        <v>1.82</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="R26" t="n">
-        <v>2.16</v>
+        <v>4.22</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.82</v>
+        <v>3.69</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="R27" t="n">
-        <v>4.22</v>
+        <v>2.16</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6947,10 +6947,10 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7144,10 +7144,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -7249,12 +7249,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46132.875</v>
+        <v>46132.89583333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="R12" t="n">
-        <v>3.37</v>
+        <v>2.99</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>2.99</v>
+        <v>3.37</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G32" t="n">

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.72</v>
+        <v>3.62</v>
       </c>
       <c r="R11" t="n">
-        <v>3.41</v>
+        <v>2.99</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="R12" t="n">
-        <v>2.99</v>
+        <v>3.41</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="R11" t="n">
-        <v>2.99</v>
+        <v>3.41</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="R13" t="n">
-        <v>3.37</v>
+        <v>2.99</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>11.2</v>
+        <v>4.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="R16" t="n">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.92</v>
+        <v>11.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.97</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.34</v>
+        <v>3.92</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.69</v>
+        <v>1.97</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="R21" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.13</v>
+        <v>3.34</v>
       </c>
       <c r="R22" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.82</v>
+        <v>3.69</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="R26" t="n">
-        <v>4.22</v>
+        <v>2.16</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.69</v>
+        <v>1.82</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="R27" t="n">
-        <v>2.16</v>
+        <v>4.22</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="R12" t="n">
-        <v>3.37</v>
+        <v>2.99</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="R13" t="n">
-        <v>2.99</v>
+        <v>3.41</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.34</v>
+        <v>3.92</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.69</v>
+        <v>1.97</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.74</v>
+        <v>4.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.92</v>
+        <v>11.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.97</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.69</v>
+        <v>1.82</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="R26" t="n">
-        <v>2.16</v>
+        <v>4.22</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.82</v>
+        <v>3.69</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="R27" t="n">
-        <v>4.22</v>
+        <v>2.16</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.72</v>
+        <v>3.62</v>
       </c>
       <c r="R13" t="n">
-        <v>3.41</v>
+        <v>2.99</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.92</v>
+        <v>4.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.97</v>
+        <v>1.58</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>11.2</v>
+        <v>4.34</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.74</v>
+        <v>3.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.13</v>
+        <v>3.34</v>
       </c>
       <c r="R21" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="R22" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6947,10 +6947,10 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7144,10 +7144,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="R11" t="n">
-        <v>3.37</v>
+        <v>2.99</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="R13" t="n">
-        <v>2.99</v>
+        <v>3.41</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.74</v>
+        <v>4.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="R16" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>11.2</v>
+        <v>3.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>1.97</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.34</v>
+        <v>11.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.69</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.82</v>
+        <v>3.69</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="R26" t="n">
-        <v>4.22</v>
+        <v>2.16</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.69</v>
+        <v>1.82</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="R27" t="n">
-        <v>2.16</v>
+        <v>4.22</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1795,40 +1795,40 @@
         <v>5.32</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE7" t="n">
         <v>1.93</v>
@@ -1837,28 +1837,28 @@
         <v>1.76</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="R11" t="n">
-        <v>2.99</v>
+        <v>3.41</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.72</v>
+        <v>3.62</v>
       </c>
       <c r="R13" t="n">
-        <v>3.41</v>
+        <v>2.99</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.34</v>
+        <v>11.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.69</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.74</v>
+        <v>3.92</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.92</v>
+        <v>4.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.97</v>
+        <v>1.58</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>11.2</v>
+        <v>4.34</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="R21" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.13</v>
+        <v>3.34</v>
       </c>
       <c r="R22" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.69</v>
+        <v>1.82</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="R26" t="n">
-        <v>2.16</v>
+        <v>4.22</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.82</v>
+        <v>3.69</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="R27" t="n">
-        <v>4.22</v>
+        <v>2.16</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6947,10 +6947,10 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7144,10 +7144,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -2189,70 +2189,70 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.34</v>
+        <v>4.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.13</v>
+        <v>3.34</v>
       </c>
       <c r="R21" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="R22" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.82</v>
+        <v>3.69</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="R26" t="n">
-        <v>4.22</v>
+        <v>2.16</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.69</v>
+        <v>1.82</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="R27" t="n">
-        <v>2.16</v>
+        <v>4.22</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6947,10 +6947,10 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7144,10 +7144,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="R8" t="n">
-        <v>8.25</v>
+        <v>6.1</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2386,70 +2386,70 @@
         <v>4.86</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="R12" t="n">
-        <v>3.37</v>
+        <v>2.99</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="R13" t="n">
-        <v>2.99</v>
+        <v>3.41</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>11.2</v>
+        <v>3.92</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="R16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BB16" t="n">
         <v>1.22</v>
       </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.92</v>
+        <v>4.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.97</v>
+        <v>1.58</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5341,40 +5341,40 @@
         <v>6.38</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AE25" t="n">
         <v>1.91</v>
@@ -5383,82 +5383,82 @@
         <v>1.82</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5735,124 +5735,124 @@
         <v>4.22</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="R11" t="n">
-        <v>3.37</v>
+        <v>2.99</v>
       </c>
       <c r="S11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X11" t="n">
         <v>2.55</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="V11" t="n">
+      <c r="Y11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.37</v>
       </c>
-      <c r="W11" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AI11" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK11" t="n">
         <v>1.62</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AM11" t="n">
         <v>1.29</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.1</v>
+        <v>3.78</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.32</v>
+        <v>2.63</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="BB11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF11" t="n">
         <v>1.22</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,94 +2771,94 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="U12" t="n">
         <v>3.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>3.16</v>
+        <v>2.94</v>
       </c>
       <c r="X12" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
         <v>2.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AI12" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK12" t="n">
         <v>1.62</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AT12" t="n">
         <v>2.83</v>
@@ -2870,34 +2870,34 @@
         <v>2.63</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AX12" t="n">
         <v>1.59</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="BD12" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,64 +3165,64 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>3.37</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="T14" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="U14" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>2.94</v>
+        <v>3.17</v>
       </c>
       <c r="X14" t="n">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA14" t="n">
         <v>1.07</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC14" t="n">
         <v>1.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="AH14" t="n">
         <v>1.36</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.05</v>
+        <v>5.3</v>
       </c>
       <c r="AJ14" t="n">
         <v>1.13</v>
@@ -3231,52 +3231,52 @@
         <v>1.62</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AM14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AQ14" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.78</v>
+        <v>3.1</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.99</v>
+        <v>1.84</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AY14" t="n">
         <v>1.33</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="BB14" t="n">
         <v>1.22</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.92</v>
+        <v>4.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.97</v>
+        <v>1.58</v>
       </c>
       <c r="S16" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.74</v>
+        <v>3.92</v>
       </c>
       <c r="Q17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>11.2</v>
+        <v>4.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.34</v>
+        <v>11.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.69</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6947,10 +6947,10 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7144,10 +7144,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,94 +2574,94 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="U11" t="n">
         <v>3.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>3.16</v>
+        <v>2.94</v>
       </c>
       <c r="X11" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
         <v>2.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AI11" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK11" t="n">
         <v>1.62</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AT11" t="n">
         <v>2.83</v>
@@ -2673,34 +2673,34 @@
         <v>2.63</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AX11" t="n">
         <v>1.59</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="BD11" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,64 +2771,64 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>3.37</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="T12" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="U12" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>2.94</v>
+        <v>3.17</v>
       </c>
       <c r="X12" t="n">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA12" t="n">
         <v>1.07</v>
       </c>
       <c r="AB12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC12" t="n">
         <v>1.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="AH12" t="n">
         <v>1.36</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.05</v>
+        <v>5.3</v>
       </c>
       <c r="AJ12" t="n">
         <v>1.13</v>
@@ -2837,52 +2837,52 @@
         <v>1.62</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AM12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AQ12" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.78</v>
+        <v>3.1</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.99</v>
+        <v>1.84</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AY12" t="n">
         <v>1.33</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="BB12" t="n">
         <v>1.22</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.72</v>
+        <v>3.62</v>
       </c>
       <c r="R13" t="n">
-        <v>3.41</v>
+        <v>2.99</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="R14" t="n">
-        <v>3.37</v>
+        <v>3.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.74</v>
+        <v>4.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="R16" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.34</v>
+        <v>11.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.69</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.69</v>
+        <v>1.82</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="R26" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC26" t="n">
         <v>2.16</v>
       </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>0</v>
-      </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.82</v>
+        <v>3.69</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="R27" t="n">
-        <v>4.22</v>
+        <v>2.16</v>
       </c>
       <c r="S27" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="R7" t="n">
-        <v>5.32</v>
+        <v>5</v>
       </c>
       <c r="S7" t="n">
         <v>2.1</v>
@@ -1807,7 +1807,7 @@
         <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="X7" t="n">
         <v>2.96</v>
@@ -1819,7 +1819,7 @@
         <v>8</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AB7" t="n">
         <v>1.06</v>
@@ -1828,16 +1828,16 @@
         <v>1.23</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AH7" t="n">
         <v>1.22</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="BD7" t="n">
         <v>3.42</v>
@@ -2210,7 +2210,7 @@
         <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="AA9" t="n">
         <v>1.05</v>
@@ -2225,28 +2225,28 @@
         <v>3.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK9" t="n">
         <v>1.74</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AM9" t="n">
         <v>1.24</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,64 +2574,64 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>3.37</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="T11" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W11" t="n">
-        <v>2.94</v>
+        <v>3.17</v>
       </c>
       <c r="X11" t="n">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA11" t="n">
         <v>1.07</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC11" t="n">
         <v>1.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="AH11" t="n">
         <v>1.36</v>
       </c>
       <c r="AI11" t="n">
-        <v>5.05</v>
+        <v>5.3</v>
       </c>
       <c r="AJ11" t="n">
         <v>1.13</v>
@@ -2640,52 +2640,52 @@
         <v>1.62</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AM11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AQ11" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.78</v>
+        <v>3.1</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.99</v>
+        <v>1.84</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AY11" t="n">
         <v>1.33</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="BB11" t="n">
         <v>1.22</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,64 +2771,64 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>3.37</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="U12" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>3.17</v>
+        <v>2.94</v>
       </c>
       <c r="X12" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z12" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA12" t="n">
         <v>1.07</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC12" t="n">
         <v>1.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="AH12" t="n">
         <v>1.36</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.3</v>
+        <v>5.05</v>
       </c>
       <c r="AJ12" t="n">
         <v>1.13</v>
@@ -2837,52 +2837,52 @@
         <v>1.62</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.1</v>
+        <v>3.78</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.32</v>
+        <v>2.63</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AY12" t="n">
         <v>1.33</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="BB12" t="n">
         <v>1.22</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S13" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.6</v>
-      </c>
       <c r="T13" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV13" t="n">
         <v>3.16</v>
       </c>
-      <c r="X13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AW13" t="n">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.88</v>
+        <v>1.54</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.18</v>
+        <v>2.79</v>
       </c>
       <c r="BB13" t="n">
         <v>1.17</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="BD13" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.72</v>
+        <v>3.62</v>
       </c>
       <c r="R14" t="n">
-        <v>3.41</v>
+        <v>2.99</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
         <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,22 +3559,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.34</v>
+        <v>4.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3583,10 +3583,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -3598,40 +3598,40 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3676,13 +3676,13 @@
         <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.92</v>
+        <v>4.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.97</v>
+        <v>1.69</v>
       </c>
       <c r="S17" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="U17" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.95</v>
+        <v>2.48</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.26</v>
+        <v>4.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="BD17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>11.2</v>
+        <v>3.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BB18" t="n">
         <v>1.22</v>
       </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.58</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4276,7 +4276,7 @@
         <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,22 +4347,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4371,10 +4371,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -4386,40 +4386,40 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,13 +4464,13 @@
         <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BF20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="R21" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.13</v>
+        <v>3.34</v>
       </c>
       <c r="R22" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.82</v>
+        <v>3.69</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="R26" t="n">
-        <v>4.22</v>
+        <v>2.16</v>
       </c>
       <c r="S26" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.69</v>
+        <v>1.82</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="R27" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC27" t="n">
         <v>2.16</v>
       </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>0</v>
-      </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,28 +6908,28 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="R33" t="n">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -6947,91 +6947,91 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
         <v>1.52</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>0</v>
       </c>
       <c r="BF33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -810,13 +810,13 @@
         <v>2.9</v>
       </c>
       <c r="S2" t="n">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="T2" t="n">
         <v>2.22</v>
       </c>
       <c r="U2" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="V2" t="n">
         <v>1.33</v>
@@ -825,7 +825,7 @@
         <v>2.88</v>
       </c>
       <c r="X2" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="Y2" t="n">
         <v>1.36</v>
@@ -837,13 +837,13 @@
         <v>1.04</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AC2" t="n">
         <v>1.24</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AE2" t="n">
         <v>1.86</v>
@@ -855,7 +855,7 @@
         <v>3.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AI2" t="n">
         <v>6.3</v>
@@ -870,49 +870,49 @@
         <v>2</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AN2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>1.55</v>
       </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="BB2" t="n">
         <v>1.25</v>
@@ -921,13 +921,13 @@
         <v>2.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="BE2" t="n">
         <v>1.67</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1395,7 +1395,7 @@
         <v>3.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
         <v>2.06</v>
@@ -1434,7 +1434,7 @@
         <v>1.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="AE5" t="n">
         <v>1.75</v>
@@ -1461,64 +1461,64 @@
         <v>2.15</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BC5" t="n">
         <v>2</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1983,19 +1983,19 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Q8" t="n">
         <v>4.45</v>
       </c>
       <c r="R8" t="n">
-        <v>6.1</v>
+        <v>7.43</v>
       </c>
       <c r="S8" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="T8" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="U8" t="n">
         <v>7</v>
@@ -2043,7 +2043,7 @@
         <v>4.55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK8" t="n">
         <v>1.88</v>
@@ -2076,10 +2076,10 @@
         <v>3.18</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="AW8" t="n">
         <v>1.84</v>
@@ -2106,7 +2106,7 @@
         <v>3.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="BF8" t="n">
         <v>1.2</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="R10" t="n">
-        <v>4.86</v>
+        <v>4.73</v>
       </c>
       <c r="S10" t="n">
         <v>2.05</v>
@@ -2395,7 +2395,7 @@
         <v>4.8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W10" t="n">
         <v>3.25</v>
@@ -2443,13 +2443,13 @@
         <v>1.6</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AM10" t="n">
         <v>1.17</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
         <v>1.16</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="BD10" t="n">
         <v>4.6</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.99</v>
+        <v>1.68</v>
       </c>
       <c r="Q11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W11" t="n">
         <v>3.6</v>
       </c>
-      <c r="R11" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3.17</v>
-      </c>
       <c r="X11" t="n">
-        <v>2.62</v>
+        <v>2.21</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>6</v>
+        <v>4.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BF11" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2771,19 +2771,19 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="S12" t="n">
         <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="U12" t="n">
         <v>3.4</v>
@@ -2792,19 +2792,19 @@
         <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="X12" t="n">
-        <v>2.33</v>
+        <v>2.59</v>
       </c>
       <c r="Y12" t="n">
         <v>1.45</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AB12" t="n">
         <v>1</v>
@@ -2837,7 +2837,7 @@
         <v>1.62</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AM12" t="n">
         <v>1.3</v>
@@ -2876,10 +2876,10 @@
         <v>1.59</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="BA12" t="n">
         <v>2.35</v>
@@ -2894,7 +2894,7 @@
         <v>3.9</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="BF12" t="n">
         <v>1.2</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.68</v>
+        <v>2.19</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="R13" t="n">
-        <v>3.9</v>
+        <v>2.95</v>
       </c>
       <c r="S13" t="n">
-        <v>2.16</v>
+        <v>2.64</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>3.16</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="W13" t="n">
-        <v>3.6</v>
+        <v>3.23</v>
       </c>
       <c r="X13" t="n">
-        <v>2.21</v>
+        <v>2.55</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.95</v>
+        <v>5.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.95</v>
+        <v>3.82</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AI13" t="n">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.86</v>
+        <v>2.13</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.45</v>
+        <v>2.83</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.16</v>
+        <v>2.63</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.32</v>
+        <v>2.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.79</v>
+        <v>2.18</v>
       </c>
       <c r="BB13" t="n">
         <v>1.17</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="R14" t="n">
+      <c r="U14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG14" t="n">
         <v>2.99</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AI14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK14" t="n">
         <v>1.62</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.78</v>
+        <v>3.1</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BC14" t="n">
         <v>1.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,22 +3756,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.34</v>
+        <v>11.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.69</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="U17" t="n">
-        <v>2.23</v>
+        <v>1.58</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3780,10 +3780,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -3795,40 +3795,40 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AD17" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,13 +3873,13 @@
         <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>4.75</v>
+        <v>1.49</v>
       </c>
       <c r="T18" t="n">
-        <v>2.18</v>
+        <v>3.35</v>
       </c>
       <c r="U18" t="n">
-        <v>2.27</v>
+        <v>7.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.56</v>
+        <v>1.63</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="Z18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM18" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AN18" t="n">
-        <v>1.2</v>
+        <v>3.65</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S19" t="n">
-        <v>1.49</v>
+        <v>4.6</v>
       </c>
       <c r="T19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AU19" t="n">
         <v>3.35</v>
       </c>
-      <c r="U19" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,22 +4347,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>11.2</v>
+        <v>4.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>2.23</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4371,10 +4371,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -4386,40 +4386,40 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,13 +4464,13 @@
         <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="BF20" t="n">
         <v>0</v>
@@ -4553,70 +4553,70 @@
         <v>2.8</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5332,19 +5332,19 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="Q25" t="n">
         <v>4.22</v>
       </c>
       <c r="R25" t="n">
-        <v>6.38</v>
+        <v>6.35</v>
       </c>
       <c r="S25" t="n">
         <v>2</v>
       </c>
       <c r="T25" t="n">
-        <v>2.06</v>
+        <v>2.35</v>
       </c>
       <c r="U25" t="n">
         <v>6</v>
@@ -5353,7 +5353,7 @@
         <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>2.89</v>
+        <v>3.01</v>
       </c>
       <c r="X25" t="n">
         <v>2.8</v>
@@ -5365,34 +5365,34 @@
         <v>6.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AB25" t="n">
         <v>1</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AG25" t="n">
         <v>3.05</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AI25" t="n">
-        <v>5.45</v>
+        <v>6.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK25" t="n">
         <v>1.95</v>
@@ -5422,10 +5422,10 @@
         <v>2.36</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="AV25" t="n">
         <v>2.39</v>
@@ -5434,10 +5434,10 @@
         <v>1.84</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AZ25" t="n">
         <v>1.35</v>
@@ -5452,7 +5452,7 @@
         <v>2.2</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="BE25" t="n">
         <v>1.62</v>
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.69</v>
+        <v>3.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.56</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="R27" t="n">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="S27" t="n">
         <v>2.45</v>
@@ -5744,10 +5744,10 @@
         <v>4.5</v>
       </c>
       <c r="V27" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W27" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="X27" t="n">
         <v>2.89</v>
@@ -5756,10 +5756,10 @@
         <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.85</v>
+        <v>8</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AB27" t="n">
         <v>1.02</v>
@@ -5783,7 +5783,7 @@
         <v>1.26</v>
       </c>
       <c r="AI27" t="n">
-        <v>6.15</v>
+        <v>8</v>
       </c>
       <c r="AJ27" t="n">
         <v>1.06</v>
@@ -5795,7 +5795,7 @@
         <v>1.85</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AN27" t="n">
         <v>1.85</v>
@@ -5813,22 +5813,22 @@
         <v>1.75</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="AT27" t="n">
         <v>3.34</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AY27" t="n">
         <v>1.24</v>
@@ -5843,7 +5843,7 @@
         <v>1.3</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="BD27" t="n">
         <v>3.25</v>
@@ -5923,28 +5923,28 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
         <v>3.25</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="T28" t="n">
         <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>4.03</v>
+        <v>3.81</v>
       </c>
       <c r="V28" t="n">
         <v>1.36</v>
       </c>
       <c r="W28" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="X28" t="n">
         <v>2.5</v>
@@ -5962,25 +5962,25 @@
         <v>1.05</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AH28" t="n">
         <v>1.33</v>
       </c>
       <c r="AI28" t="n">
-        <v>5.35</v>
+        <v>5.4</v>
       </c>
       <c r="AJ28" t="n">
         <v>1.11</v>
@@ -5995,7 +5995,7 @@
         <v>1.33</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6010,22 +6010,22 @@
         <v>1.68</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="AT28" t="n">
         <v>2.38</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.79</v>
+        <v>4.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AY28" t="n">
         <v>1.5</v>
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="Q29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S29" t="n">
         <v>3.35</v>
       </c>
-      <c r="R29" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="S2" t="n">
         <v>2.57</v>
@@ -819,10 +819,10 @@
         <v>3.58</v>
       </c>
       <c r="V2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="X2" t="n">
         <v>2.82</v>
@@ -834,7 +834,7 @@
         <v>6.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AB2" t="n">
         <v>1.05</v>
@@ -843,7 +843,7 @@
         <v>1.24</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AE2" t="n">
         <v>1.86</v>
@@ -855,7 +855,7 @@
         <v>3.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AI2" t="n">
         <v>6.3</v>
@@ -870,7 +870,7 @@
         <v>2</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AN2" t="n">
         <v>1.57</v>
@@ -882,7 +882,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR2" t="n">
         <v>2.1</v>
@@ -897,7 +897,7 @@
         <v>3.32</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="AW2" t="n">
         <v>1.85</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
         <v>3.4</v>
@@ -1404,7 +1404,7 @@
         <v>3.61</v>
       </c>
       <c r="T5" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
         <v>2.63</v>
@@ -1422,7 +1422,7 @@
         <v>1.43</v>
       </c>
       <c r="Z5" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA5" t="n">
         <v>1.07</v>
@@ -1431,7 +1431,7 @@
         <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AD5" t="n">
         <v>3.9</v>
@@ -1452,7 +1452,7 @@
         <v>4.85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK5" t="n">
         <v>1.62</v>
@@ -1476,37 +1476,37 @@
         <v>1.41</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="AV5" t="n">
         <v>2.59</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="BA5" t="n">
         <v>2.11</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BC5" t="n">
         <v>2</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.46</v>
+        <v>3.73</v>
       </c>
       <c r="R12" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="T12" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="U12" t="n">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="X12" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.9</v>
+        <v>5.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AB12" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
         <v>2.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.05</v>
+        <v>4.75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK12" t="n">
         <v>1.62</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2855,10 +2855,10 @@
         <v>1.39</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AT12" t="n">
         <v>2.83</v>
@@ -2870,34 +2870,34 @@
         <v>2.63</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AX12" t="n">
         <v>1.59</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="BB12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF12" t="n">
         <v>1.22</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.73</v>
+        <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>2.95</v>
+        <v>3.48</v>
       </c>
       <c r="S13" t="n">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="T13" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="U13" t="n">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>3.23</v>
+        <v>2.85</v>
       </c>
       <c r="X13" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.55</v>
+        <v>6</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.82</v>
+        <v>3.54</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.75</v>
+        <v>5.1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK13" t="n">
         <v>1.62</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BB13" t="n">
         <v>1.19</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.17</v>
       </c>
       <c r="BC13" t="n">
         <v>1.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,64 +3165,64 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="R14" t="n">
-        <v>3.48</v>
+        <v>3.18</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="X14" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Z14" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AC14" t="n">
         <v>1.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="AH14" t="n">
         <v>1.36</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="AJ14" t="n">
         <v>1.13</v>
@@ -3237,61 +3237,61 @@
         <v>1.3</v>
       </c>
       <c r="AN14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE14" t="n">
         <v>1.73</v>
       </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.77</v>
-      </c>
       <c r="BF14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.74</v>
+        <v>3.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="S16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T16" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="U16" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS16" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
+      <c r="AT16" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BB16" t="n">
         <v>1.16</v>
       </c>
-      <c r="AD16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
       <c r="BC16" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,22 +3756,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>11.2</v>
+        <v>4.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="U17" t="n">
-        <v>1.58</v>
+        <v>2.23</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3780,10 +3780,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -3795,40 +3795,40 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,13 +3873,13 @@
         <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,22 +3953,22 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S18" t="n">
-        <v>1.49</v>
+        <v>4.7</v>
       </c>
       <c r="T18" t="n">
-        <v>3.35</v>
+        <v>2.45</v>
       </c>
       <c r="U18" t="n">
-        <v>7.5</v>
+        <v>2.05</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3977,10 +3977,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3992,40 +3992,40 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.21</v>
+        <v>1.55</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.65</v>
+        <v>2.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.28</v>
+        <v>4.1</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.06</v>
+        <v>2.1</v>
       </c>
       <c r="AN18" t="n">
-        <v>3.65</v>
+        <v>1.11</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4070,16 +4070,16 @@
         <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>4.6</v>
+        <v>1.49</v>
       </c>
       <c r="T19" t="n">
-        <v>2.18</v>
+        <v>3.35</v>
       </c>
       <c r="U19" t="n">
-        <v>2.27</v>
+        <v>7.5</v>
       </c>
       <c r="V19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.56</v>
+        <v>1.63</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM19" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AN19" t="n">
-        <v>1.18</v>
+        <v>3.65</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,22 +4347,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.34</v>
+        <v>11.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.69</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="T20" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="U20" t="n">
-        <v>2.23</v>
+        <v>1.58</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4371,10 +4371,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -4386,40 +4386,40 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AD20" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AI20" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,13 +4464,13 @@
         <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="BF20" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G32" t="n">

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Q7" t="n">
         <v>3.8</v>
@@ -1795,16 +1795,16 @@
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="U7" t="n">
         <v>5.75</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
         <v>2.59</v>
@@ -1816,16 +1816,16 @@
         <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AA7" t="n">
         <v>1.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AD7" t="n">
         <v>3</v>
@@ -1852,7 +1852,7 @@
         <v>2.05</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AM7" t="n">
         <v>1.25</v>
@@ -1906,7 +1906,7 @@
         <v>2.24</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="BE7" t="n">
         <v>1.53</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD11" t="n">
         <v>3.75</v>
       </c>
-      <c r="R11" t="n">
+      <c r="AE11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD11" t="n">
         <v>3.9</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BE11" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.73</v>
+        <v>3.3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.95</v>
+        <v>3.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="T12" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="U12" t="n">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>3.23</v>
+        <v>2.85</v>
       </c>
       <c r="X12" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.55</v>
+        <v>6</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.82</v>
+        <v>3.54</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.75</v>
+        <v>5.1</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK12" t="n">
         <v>1.62</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BB12" t="n">
         <v>1.19</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.17</v>
       </c>
       <c r="BC12" t="n">
         <v>1.9</v>
       </c>
       <c r="BD12" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.3</v>
+        <v>3.73</v>
       </c>
       <c r="R13" t="n">
-        <v>3.48</v>
+        <v>2.95</v>
       </c>
       <c r="S13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="X13" t="n">
         <v>2.55</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V13" t="n">
+      <c r="Y13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.37</v>
       </c>
-      <c r="W13" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AI13" t="n">
-        <v>5.1</v>
+        <v>4.75</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK13" t="n">
         <v>1.62</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.1</v>
+        <v>3.78</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.32</v>
+        <v>2.63</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="BC13" t="n">
         <v>1.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.46</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
-        <v>3.18</v>
+        <v>3.9</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="T14" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="U14" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="W14" t="n">
-        <v>3.21</v>
+        <v>3.6</v>
       </c>
       <c r="X14" t="n">
-        <v>2.59</v>
+        <v>2.21</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.9</v>
+        <v>4.95</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AC14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BF14" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,22 +3756,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>1.49</v>
       </c>
       <c r="T17" t="n">
-        <v>2.35</v>
+        <v>3.35</v>
       </c>
       <c r="U17" t="n">
-        <v>2.23</v>
+        <v>7.5</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3780,55 +3780,55 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI17" t="n">
         <v>2.28</v>
       </c>
-      <c r="Y17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.15</v>
+        <v>3.65</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,16 +3873,16 @@
         <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.74</v>
+        <v>11.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="R18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S18" t="n">
+        <v>8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.58</v>
       </c>
-      <c r="S18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF18" t="n">
         <v>2.45</v>
       </c>
-      <c r="U18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AG18" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="AM18" t="n">
-        <v>2.1</v>
+        <v>1.08</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4070,13 +4070,13 @@
         <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="BF18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,22 +4150,22 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S19" t="n">
-        <v>1.49</v>
+        <v>4.7</v>
       </c>
       <c r="T19" t="n">
-        <v>3.35</v>
+        <v>2.45</v>
       </c>
       <c r="U19" t="n">
-        <v>7.5</v>
+        <v>2.05</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4174,10 +4174,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -4189,40 +4189,40 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.21</v>
+        <v>1.55</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.65</v>
+        <v>2.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.28</v>
+        <v>4.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.06</v>
+        <v>2.1</v>
       </c>
       <c r="AN19" t="n">
-        <v>3.65</v>
+        <v>1.11</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4267,16 +4267,16 @@
         <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,22 +4347,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>11.2</v>
+        <v>4.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>2.23</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4371,10 +4371,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -4386,40 +4386,40 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,13 +4464,13 @@
         <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="BF20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X21" t="n">
         <v>2.8</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3</v>
-      </c>
-      <c r="V21" t="n">
+      <c r="Y21" t="n">
         <v>1.35</v>
       </c>
-      <c r="W21" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.33</v>
-      </c>
       <c r="Z21" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AC21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM21" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD21" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AN21" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="R22" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="S22" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="T22" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
+        <v>3</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD22" t="n">
         <v>3.4</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BE22" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY32" t="n">
         <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -807,10 +807,10 @@
         <v>3.52</v>
       </c>
       <c r="R2" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="T2" t="n">
         <v>2.22</v>
@@ -819,10 +819,10 @@
         <v>3.58</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="X2" t="n">
         <v>2.82</v>
@@ -834,13 +834,13 @@
         <v>6.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AB2" t="n">
         <v>1.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AD2" t="n">
         <v>3.4</v>
@@ -870,10 +870,10 @@
         <v>2</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -882,28 +882,28 @@
         <v>1.24</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AY2" t="n">
         <v>1.27</v>
@@ -915,19 +915,19 @@
         <v>3.32</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BC2" t="n">
         <v>2.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.3</v>
+        <v>3.73</v>
       </c>
       <c r="R12" t="n">
-        <v>3.48</v>
+        <v>2.95</v>
       </c>
       <c r="S12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="X12" t="n">
         <v>2.55</v>
       </c>
-      <c r="T12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V12" t="n">
+      <c r="Y12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.37</v>
       </c>
-      <c r="W12" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AI12" t="n">
-        <v>5.1</v>
+        <v>4.75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK12" t="n">
         <v>1.62</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.1</v>
+        <v>3.78</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.32</v>
+        <v>2.63</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="BC12" t="n">
         <v>1.9</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.19</v>
+        <v>1.68</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="R13" t="n">
-        <v>2.95</v>
+        <v>4.1</v>
       </c>
       <c r="S13" t="n">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="U13" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV13" t="n">
         <v>3.16</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AW13" t="n">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.59</v>
+        <v>1.84</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.18</v>
+        <v>2.79</v>
       </c>
       <c r="BB13" t="n">
         <v>1.17</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="BD13" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>3.9</v>
+        <v>3.48</v>
       </c>
       <c r="S14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.16</v>
       </c>
-      <c r="T14" t="n">
-        <v>2.4</v>
-      </c>
       <c r="U14" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="V14" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="X14" t="n">
-        <v>2.21</v>
+        <v>2.62</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.95</v>
+        <v>6</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.95</v>
+        <v>3.54</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BA14" t="n">
         <v>2.3</v>
       </c>
-      <c r="AH14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.79</v>
-      </c>
       <c r="BB14" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.6</v>
+        <v>3.98</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3365,16 +3365,16 @@
         <v>2.64</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="S15" t="n">
-        <v>2.93</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="U15" t="n">
         <v>2.9</v>
@@ -3389,13 +3389,13 @@
         <v>2.75</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AB15" t="n">
         <v>1</v>
@@ -3404,25 +3404,25 @@
         <v>1.28</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG15" t="n">
         <v>2.92</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AI15" t="n">
         <v>6</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK15" t="n">
         <v>1.62</v>
@@ -3440,55 +3440,55 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AR15" t="n">
         <v>2.1</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.34</v>
+        <v>3.84</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.41</v>
+        <v>2.67</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BC15" t="n">
         <v>2</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BE15" t="n">
         <v>1.73</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.8</v>
+        <v>4.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R16" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="S16" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="U16" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="Z16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.95</v>
+        <v>2.48</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.26</v>
+        <v>4.3</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S17" t="n">
-        <v>1.49</v>
+        <v>4.6</v>
       </c>
       <c r="T17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AU17" t="n">
         <v>3.35</v>
       </c>
-      <c r="U17" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,22 +3953,22 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>11.2</v>
+        <v>4.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>4.7</v>
       </c>
       <c r="T18" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="U18" t="n">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3977,55 +3977,55 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK18" t="n">
         <v>1.62</v>
       </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG18" t="n">
+      <c r="AL18" t="n">
         <v>2.12</v>
       </c>
-      <c r="AH18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AM18" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4070,13 +4070,13 @@
         <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="BF18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.58</v>
       </c>
-      <c r="S19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
+      <c r="AH19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL19" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AM19" t="n">
-        <v>2.1</v>
+        <v>1.06</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.11</v>
+        <v>3.65</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4267,16 +4267,16 @@
         <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,22 +4347,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.34</v>
+        <v>11.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.69</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="T20" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="U20" t="n">
-        <v>2.23</v>
+        <v>1.58</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4371,10 +4371,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -4386,40 +4386,40 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AD20" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AI20" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,13 +4464,13 @@
         <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="BF20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="R21" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="T21" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
+        <v>3</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD21" t="n">
         <v>3.4</v>
       </c>
-      <c r="V21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BE21" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X22" t="n">
         <v>2.8</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3</v>
-      </c>
-      <c r="V22" t="n">
+      <c r="Y22" t="n">
         <v>1.35</v>
       </c>
-      <c r="W22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.33</v>
-      </c>
       <c r="Z22" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AC22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM22" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD22" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AN22" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,130 +5529,130 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="Q26" t="n">
         <v>3.25</v>
       </c>
       <c r="R26" t="n">
-        <v>2.12</v>
+        <v>4</v>
       </c>
       <c r="S26" t="n">
-        <v>3.68</v>
+        <v>2.45</v>
       </c>
       <c r="T26" t="n">
         <v>2.1</v>
       </c>
       <c r="U26" t="n">
-        <v>2.81</v>
+        <v>4.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W26" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="X26" t="n">
-        <v>3.21</v>
+        <v>2.89</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z26" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.86</v>
+        <v>3.72</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AI26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL26" t="n">
         <v>1.85</v>
       </c>
-      <c r="AL26" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AM26" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AN26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB26" t="n">
         <v>1.3</v>
       </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BC26" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BF26" t="n">
         <v>1.13</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,130 +5726,130 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="Q27" t="n">
         <v>3.25</v>
       </c>
       <c r="R27" t="n">
-        <v>4</v>
+        <v>2.12</v>
       </c>
       <c r="S27" t="n">
-        <v>2.45</v>
+        <v>3.68</v>
       </c>
       <c r="T27" t="n">
         <v>2.1</v>
       </c>
       <c r="U27" t="n">
-        <v>4.5</v>
+        <v>2.81</v>
       </c>
       <c r="V27" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W27" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="X27" t="n">
-        <v>2.89</v>
+        <v>3.21</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z27" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB27" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB27" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AC27" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="AE27" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.72</v>
+        <v>3.86</v>
       </c>
       <c r="AH27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
         <v>1.26</v>
       </c>
-      <c r="AI27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
+      <c r="AQ27" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AY27" t="n">
         <v>1.27</v>
       </c>
-      <c r="AQ27" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AZ27" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.9</v>
+        <v>1.97</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="BF27" t="n">
         <v>1.13</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
         <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AQ33" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q33" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R33" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U33" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ33" t="n">
+      <c r="AR33" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BF33" t="n">
         <v>1.06</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="R34" t="n">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="S34" t="n">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="T34" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="U34" t="n">
-        <v>4.75</v>
+        <v>4.35</v>
       </c>
       <c r="V34" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="W34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
         <v>2.2</v>
       </c>
-      <c r="X34" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC34" t="n">
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
         <v>1.52</v>
       </c>
-      <c r="AD34" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BF34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>6.29</v>
+        <v>6.19</v>
       </c>
       <c r="S35" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="T35" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="U35" t="n">
-        <v>6.17</v>
+        <v>6.12</v>
       </c>
       <c r="V35" t="n">
         <v>1.33</v>
       </c>
       <c r="W35" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="X35" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z35" t="n">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="AA35" t="n">
         <v>1.06</v>
       </c>
       <c r="AB35" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AF35" t="n">
         <v>2</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.03</v>
+        <v>2.83</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AI35" t="n">
-        <v>5.4</v>
+        <v>6.1</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AN35" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.06</v>
+        <v>2.42</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.63</v>
+        <v>3.28</v>
       </c>
       <c r="AU35" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AW35" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="BA35" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BC35" t="n">
         <v>2.12</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="R2" t="n">
         <v>3</v>
@@ -813,16 +813,16 @@
         <v>2.75</v>
       </c>
       <c r="T2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U2" t="n">
-        <v>3.58</v>
+        <v>3.63</v>
       </c>
       <c r="V2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="X2" t="n">
         <v>2.82</v>
@@ -831,37 +831,37 @@
         <v>1.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="AA2" t="n">
         <v>1.04</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC2" t="n">
         <v>1.28</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AF2" t="n">
         <v>1.85</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AI2" t="n">
         <v>6.3</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AK2" t="n">
         <v>1.73</v>
@@ -870,7 +870,7 @@
         <v>2</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AN2" t="n">
         <v>1.55</v>
@@ -882,34 +882,34 @@
         <v>1.24</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AY2" t="n">
         <v>1.27</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BA2" t="n">
         <v>3.32</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1986,34 +1986,34 @@
         <v>1.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.45</v>
+        <v>4.35</v>
       </c>
       <c r="R8" t="n">
-        <v>7.43</v>
+        <v>7.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="T8" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="U8" t="n">
         <v>7</v>
       </c>
       <c r="V8" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X8" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="Y8" t="n">
         <v>1.47</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA8" t="n">
         <v>1.08</v>
@@ -2025,13 +2025,13 @@
         <v>1.23</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.22</v>
+        <v>3.84</v>
       </c>
       <c r="AE8" t="n">
         <v>1.69</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AG8" t="n">
         <v>2.56</v>
@@ -2040,22 +2040,22 @@
         <v>1.4</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK8" t="n">
         <v>1.88</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2064,49 +2064,49 @@
         <v>1.25</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.18</v>
+        <v>2.81</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.28</v>
+        <v>3.72</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.35</v>
+        <v>7.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BC8" t="n">
         <v>1.89</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="BF8" t="n">
         <v>1.2</v>
@@ -2210,7 +2210,7 @@
         <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="AA9" t="n">
         <v>1.05</v>
@@ -2225,28 +2225,28 @@
         <v>3.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AI9" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK9" t="n">
         <v>1.74</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AM9" t="n">
         <v>1.24</v>
@@ -2377,16 +2377,16 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
         <v>4.73</v>
       </c>
       <c r="S10" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="T10" t="n">
         <v>2.4</v>
@@ -2401,100 +2401,100 @@
         <v>3.25</v>
       </c>
       <c r="X10" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Y10" t="n">
         <v>1.48</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AB10" t="n">
         <v>1.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
         <v>1.66</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AG10" t="n">
         <v>2.59</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AI10" t="n">
         <v>4.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AM10" t="n">
         <v>1.17</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BB10" t="n">
         <v>1.16</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="BD10" t="n">
         <v>4.6</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,64 +2574,64 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="R11" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="T11" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="U11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
         <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="X11" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.9</v>
+        <v>6.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI11" t="n">
-        <v>5.05</v>
+        <v>5.15</v>
       </c>
       <c r="AJ11" t="n">
         <v>1.13</v>
@@ -2640,67 +2640,67 @@
         <v>1.62</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AM11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY11" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BC11" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2771,55 +2771,55 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.73</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="S12" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>3.16</v>
+        <v>3.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="X12" t="n">
         <v>2.55</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Z12" t="n">
         <v>5.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
         <v>1.24</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AG12" t="n">
         <v>2.8</v>
@@ -2831,7 +2831,7 @@
         <v>4.75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AK12" t="n">
         <v>1.62</v>
@@ -2849,46 +2849,46 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AS12" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW12" t="n">
         <v>2.13</v>
       </c>
-      <c r="AT12" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AX12" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BD12" t="n">
         <v>4</v>
@@ -2968,40 +2968,40 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="R13" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="T13" t="n">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="U13" t="n">
-        <v>4.35</v>
+        <v>4.44</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
         <v>3.6</v>
       </c>
       <c r="X13" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Z13" t="n">
         <v>4.95</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AB13" t="n">
         <v>1.02</v>
@@ -3010,37 +3010,37 @@
         <v>1.14</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.95</v>
+        <v>4.75</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AG13" t="n">
         <v>2.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI13" t="n">
         <v>3.9</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3085,16 +3085,16 @@
         <v>1.17</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="BD13" t="n">
         <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,43 +3165,43 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="R14" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.16</v>
+        <v>2.35</v>
       </c>
       <c r="U14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W14" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="X14" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Z14" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="AA14" t="n">
         <v>1.07</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC14" t="n">
         <v>1.25</v>
@@ -3210,88 +3210,88 @@
         <v>3.54</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.99</v>
+        <v>2.76</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL14" t="n">
         <v>2.1</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AN14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BE14" t="n">
         <v>1.73</v>
       </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.77</v>
-      </c>
       <c r="BF14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.34</v>
+        <v>4.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="S16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD16" t="n">
         <v>4.2</v>
       </c>
-      <c r="T16" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>4</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3676,13 +3676,13 @@
         <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>4.6</v>
+        <v>1.49</v>
       </c>
       <c r="T17" t="n">
-        <v>2.18</v>
+        <v>3.35</v>
       </c>
       <c r="U17" t="n">
-        <v>2.27</v>
+        <v>7.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.56</v>
+        <v>1.63</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM17" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AN17" t="n">
-        <v>1.18</v>
+        <v>3.65</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.74</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="S18" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="T18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AV18" t="n">
         <v>2.45</v>
       </c>
-      <c r="U18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y18" t="n">
+      <c r="AW18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX18" t="n">
         <v>1.52</v>
       </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,22 +4150,22 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>1.49</v>
+        <v>8</v>
       </c>
       <c r="T19" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="U19" t="n">
-        <v>7.5</v>
+        <v>1.58</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4174,10 +4174,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -4189,40 +4189,40 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.21</v>
+        <v>1.45</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.65</v>
+        <v>2.45</v>
       </c>
       <c r="AG19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.58</v>
       </c>
-      <c r="AH19" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AI19" t="n">
-        <v>2.28</v>
+        <v>3.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AN19" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4267,16 +4267,16 @@
         <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,22 +4347,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>11.2</v>
+        <v>4.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>2.23</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4371,10 +4371,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -4386,40 +4386,40 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,13 +4464,13 @@
         <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="BF20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X21" t="n">
         <v>2.8</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3</v>
-      </c>
-      <c r="V21" t="n">
+      <c r="Y21" t="n">
         <v>1.35</v>
       </c>
-      <c r="W21" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.33</v>
-      </c>
       <c r="Z21" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AC21" t="n">
         <v>1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AG21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BD21" t="n">
         <v>3.58</v>
       </c>
-      <c r="AH21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BE21" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="R22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W22" t="n">
         <v>2.56</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T22" t="n">
+      <c r="X22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE22" t="n">
         <v>2.15</v>
       </c>
-      <c r="U22" t="n">
+      <c r="AF22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BD22" t="n">
         <v>3.4</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BE22" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5332,40 +5332,40 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.22</v>
+        <v>3.8</v>
       </c>
       <c r="R25" t="n">
-        <v>6.35</v>
+        <v>5.9</v>
       </c>
       <c r="S25" t="n">
         <v>2</v>
       </c>
       <c r="T25" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="V25" t="n">
         <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="X25" t="n">
         <v>2.8</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.2</v>
+        <v>6.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AB25" t="n">
         <v>1</v>
@@ -5380,16 +5380,16 @@
         <v>1.86</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AG25" t="n">
         <v>3.05</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AI25" t="n">
-        <v>6.5</v>
+        <v>6.82</v>
       </c>
       <c r="AJ25" t="n">
         <v>1.1</v>
@@ -5401,7 +5401,7 @@
         <v>1.73</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AN25" t="n">
         <v>2.45</v>
@@ -5410,37 +5410,37 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BA25" t="n">
         <v>3.85</v>
@@ -5452,10 +5452,10 @@
         <v>2.2</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="BF25" t="n">
         <v>1.15</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>4</v>
+        <v>2.12</v>
       </c>
       <c r="S26" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="T26" t="n">
         <v>2.1</v>
       </c>
       <c r="U26" t="n">
-        <v>4.5</v>
+        <v>2.63</v>
       </c>
       <c r="V26" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W26" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="X26" t="n">
-        <v>2.89</v>
+        <v>3.21</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB26" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AC26" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AD26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU26" t="n">
         <v>3.1</v>
       </c>
-      <c r="AE26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.14</v>
-      </c>
       <c r="AV26" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AW26" t="n">
         <v>1.78</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,130 +5726,130 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="Q27" t="n">
         <v>3.25</v>
       </c>
       <c r="R27" t="n">
-        <v>2.12</v>
+        <v>4</v>
       </c>
       <c r="S27" t="n">
-        <v>3.68</v>
+        <v>2.45</v>
       </c>
       <c r="T27" t="n">
         <v>2.1</v>
       </c>
       <c r="U27" t="n">
-        <v>2.81</v>
+        <v>4.5</v>
       </c>
       <c r="V27" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W27" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="X27" t="n">
-        <v>3.21</v>
+        <v>2.89</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.86</v>
+        <v>3.72</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AI27" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL27" t="n">
         <v>1.85</v>
       </c>
-      <c r="AL27" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AM27" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AN27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB27" t="n">
         <v>1.3</v>
       </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BC27" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BF27" t="n">
         <v>1.13</v>
@@ -5923,70 +5923,70 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R28" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="S28" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="T28" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="U28" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="V28" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W28" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="X28" t="n">
         <v>2.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="AA28" t="n">
         <v>1.08</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AF28" t="n">
         <v>1.9</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AH28" t="n">
         <v>1.33</v>
       </c>
       <c r="AI28" t="n">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="AJ28" t="n">
         <v>1.11</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AL28" t="n">
         <v>2.1</v>
@@ -5995,55 +5995,55 @@
         <v>1.33</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AR28" t="n">
         <v>1.68</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AU28" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AV28" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AW28" t="n">
         <v>2.17</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="BA28" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC28" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BE28" t="n">
         <v>1.7</v>
@@ -6126,7 +6126,7 @@
         <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="S29" t="n">
         <v>3.35</v>
@@ -6138,10 +6138,10 @@
         <v>2.8</v>
       </c>
       <c r="V29" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W29" t="n">
-        <v>3.08</v>
+        <v>2.73</v>
       </c>
       <c r="X29" t="n">
         <v>2.73</v>
@@ -6150,100 +6150,100 @@
         <v>1.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AB29" t="n">
         <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="AH29" t="n">
         <v>1.3</v>
       </c>
       <c r="AI29" t="n">
-        <v>5.55</v>
+        <v>6.25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK29" t="n">
         <v>1.68</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AM29" t="n">
         <v>1.33</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.64</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.44</v>
+        <v>2.07</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="AU29" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AY29" t="n">
         <v>1.18</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2.53</v>
+        <v>2.24</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BC29" t="n">
         <v>2.07</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="BF29" t="n">
         <v>1.17</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G32" t="n">

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI35"/>
+  <dimension ref="A1:BI36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -819,13 +819,13 @@
         <v>3.63</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="X2" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="Y2" t="n">
         <v>1.36</v>
@@ -840,7 +840,7 @@
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AD2" t="n">
         <v>3.34</v>
@@ -852,7 +852,7 @@
         <v>1.85</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="AH2" t="n">
         <v>1.27</v>
@@ -882,13 +882,13 @@
         <v>1.24</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR2" t="n">
         <v>2.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="AT2" t="n">
         <v>3.15</v>
@@ -897,7 +897,7 @@
         <v>3.32</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="AW2" t="n">
         <v>1.85</v>
@@ -945,27 +945,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
-        <v>46132.35416666666</v>
+        <v>46132.29166666666</v>
       </c>
     </row>
     <row r="4">
@@ -1142,27 +1142,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
-        <v>46132.375</v>
+        <v>46132.35416666666</v>
       </c>
     </row>
     <row r="5">
@@ -1410,16 +1410,16 @@
         <v>2.63</v>
       </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>3.24</v>
+        <v>2.86</v>
       </c>
       <c r="X5" t="n">
         <v>2.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="Z5" t="n">
         <v>5.75</v>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="BI7" s="3" t="n">
-        <v>46132.45833333334</v>
+        <v>46132.41666666666</v>
       </c>
     </row>
     <row r="8">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,134 +1983,134 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
+        <v>5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI8" t="n">
         <v>7.1</v>
       </c>
-      <c r="S8" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U8" t="n">
-        <v>7</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>5</v>
-      </c>
       <c r="AJ8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BF8" t="n">
         <v>1.13</v>
       </c>
-      <c r="AK8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BG8" t="n">
         <v>0</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="BI8" s="3" t="n">
-        <v>46132.47916666666</v>
+        <v>46132.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="S9" t="n">
-        <v>2.53</v>
+        <v>1.89</v>
       </c>
       <c r="T9" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="U9" t="n">
-        <v>4.28</v>
+        <v>7</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="X9" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.55</v>
+        <v>5.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.14</v>
+        <v>3.84</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.79</v>
+        <v>2.11</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.14</v>
+        <v>2.56</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.95</v>
+        <v>5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.68</v>
+        <v>2.85</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.58</v>
+        <v>4.33</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="3" t="n">
-        <v>46132.5</v>
+        <v>46132.47916666666</v>
       </c>
     </row>
     <row r="10">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.98</v>
+        <v>2.53</v>
       </c>
       <c r="T10" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>4.8</v>
+        <v>4.28</v>
       </c>
       <c r="V10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC10" t="n">
         <v>1.27</v>
       </c>
-      <c r="W10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.12</v>
+        <v>1.79</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.59</v>
+        <v>3.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AI10" t="n">
-        <v>4.8</v>
+        <v>5.95</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.6</v>
+        <v>3.58</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>46132.54166666666</v>
+        <v>46132.5</v>
       </c>
     </row>
     <row r="11">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF11" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG11" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" t="n">
-        <v>5.15</v>
+        <v>4.75</v>
       </c>
       <c r="AJ11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
         <v>1.13</v>
       </c>
-      <c r="AK11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AQ11" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.06</v>
+        <v>1.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.31</v>
+        <v>1.97</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.97</v>
+        <v>2.37</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.77</v>
+        <v>1.35</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.3</v>
+        <v>3.68</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46132.58333333334</v>
+        <v>46132.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -2831,7 +2831,7 @@
         <v>4.75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AK12" t="n">
         <v>1.62</v>
@@ -2849,34 +2849,34 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AZ12" t="n">
         <v>1.88</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.9</v>
+        <v>3.42</v>
       </c>
       <c r="R13" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="S13" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="U13" t="n">
-        <v>4.44</v>
+        <v>3.4</v>
       </c>
       <c r="V13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC13" t="n">
         <v>1.25</v>
       </c>
-      <c r="W13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AD13" t="n">
-        <v>4.75</v>
+        <v>3.54</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.3</v>
+        <v>2.76</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AI13" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AJ13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BB13" t="n">
         <v>1.2</v>
       </c>
-      <c r="AK13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AM13" t="n">
+      <c r="BC13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BF13" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="R14" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="T14" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2.35</v>
       </c>
-      <c r="U14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC14" t="n">
+      <c r="AG14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BF14" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3309,27 +3309,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.64</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U15" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="X15" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.7</v>
+        <v>6.05</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.05</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1</v>
       </c>
       <c r="AC15" t="n">
         <v>1.28</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.58</v>
+        <v>3.44</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" t="n">
-        <v>6</v>
+        <v>5.15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
         <v>1.62</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BB15" t="n">
         <v>1.18</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BC15" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46132.58680555555</v>
+        <v>46132.58333333334</v>
       </c>
     </row>
     <row r="16">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,134 +3559,134 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.74</v>
+        <v>2.64</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
-        <v>1.58</v>
+        <v>2.5</v>
       </c>
       <c r="S16" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="U16" t="n">
-        <v>2.05</v>
+        <v>2.9</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X16" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.38</v>
+        <v>2.92</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AK16" t="n">
         <v>1.62</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AM16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BF16" t="n">
         <v>1.16</v>
       </c>
-      <c r="AN16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>0</v>
-      </c>
       <c r="BG16" t="n">
         <v>0</v>
       </c>
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46132.60416666666</v>
+        <v>46132.58680555555</v>
       </c>
     </row>
     <row r="17">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="Q18" t="n">
         <v>4</v>
       </c>
-      <c r="Q18" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R18" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="S18" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="T18" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="U18" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="V18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="Z18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN18" t="n">
         <v>1.11</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>11.2</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="R19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BB19" t="n">
         <v>1.22</v>
       </c>
-      <c r="S19" t="n">
-        <v>8</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK19" t="n">
+      <c r="BC19" t="n">
         <v>1.95</v>
       </c>
-      <c r="AL19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,22 +4347,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.34</v>
+        <v>11.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.69</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="T20" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="U20" t="n">
-        <v>2.23</v>
+        <v>1.58</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4371,10 +4371,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -4386,40 +4386,40 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AD20" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AI20" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,13 +4464,13 @@
         <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="BF20" t="n">
         <v>0</v>
@@ -4491,27 +4491,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>4.34</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="R21" t="n">
-        <v>2.56</v>
+        <v>1.69</v>
       </c>
       <c r="S21" t="n">
-        <v>2.85</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="U21" t="n">
-        <v>3.4</v>
+        <v>2.23</v>
       </c>
       <c r="V21" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.5</v>
+        <v>2.48</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AI21" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.97</v>
+        <v>2.17</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.21</v>
+        <v>1.79</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46132.61458333334</v>
+        <v>46132.60416666666</v>
       </c>
     </row>
     <row r="22">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X22" t="n">
         <v>2.8</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3</v>
-      </c>
-      <c r="V22" t="n">
+      <c r="Y22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN22" t="n">
         <v>1.44</v>
       </c>
-      <c r="W22" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC22" t="n">
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AY22" t="n">
         <v>1.29</v>
       </c>
-      <c r="AD22" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG22" t="n">
+      <c r="AZ22" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BD22" t="n">
         <v>3.58</v>
       </c>
-      <c r="AH22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BE22" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46132.625</v>
+        <v>46132.61458333334</v>
       </c>
     </row>
     <row r="24">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>5.9</v>
+        <v>3.85</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>5.9</v>
+        <v>3.5</v>
       </c>
       <c r="V25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AZ25" t="n">
         <v>1.4</v>
       </c>
-      <c r="W25" t="n">
-        <v>3</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>6.82</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BA25" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.2</v>
+        <v>1.64</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46132.64583333334</v>
+        <v>46132.625</v>
       </c>
     </row>
     <row r="26">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.5</v>
+        <v>1.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R26" t="n">
-        <v>2.12</v>
+        <v>5.9</v>
       </c>
       <c r="S26" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U26" t="n">
-        <v>2.63</v>
+        <v>5.75</v>
       </c>
       <c r="V26" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W26" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="X26" t="n">
-        <v>3.21</v>
+        <v>2.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="Z26" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AA26" t="n">
         <v>1.06</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AD26" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.86</v>
+        <v>3.05</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AI26" t="n">
-        <v>7.8</v>
+        <v>6.82</v>
       </c>
       <c r="AJ26" t="n">
         <v>1.08</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.3</v>
+        <v>2.45</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.22</v>
+        <v>1.81</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AY26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB26" t="n">
         <v>1.29</v>
       </c>
-      <c r="AZ26" t="n">
+      <c r="BC26" t="n">
         <v>2.2</v>
       </c>
-      <c r="BA26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.38</v>
-      </c>
       <c r="BD26" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46132.65625</v>
+        <v>46132.64583333334</v>
       </c>
     </row>
     <row r="27">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>4</v>
+        <v>2.12</v>
       </c>
       <c r="S27" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="T27" t="n">
         <v>2.1</v>
       </c>
       <c r="U27" t="n">
-        <v>4.5</v>
+        <v>2.63</v>
       </c>
       <c r="V27" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W27" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="X27" t="n">
-        <v>2.89</v>
+        <v>3.21</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB27" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB27" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AC27" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.72</v>
+        <v>3.86</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AI27" t="n">
         <v>8</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AW27" t="n">
         <v>1.78</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.36</v>
+        <v>1.77</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>2.89</v>
+        <v>4</v>
       </c>
       <c r="S28" t="n">
-        <v>3.04</v>
+        <v>2.45</v>
       </c>
       <c r="T28" t="n">
-        <v>2.31</v>
+        <v>2.03</v>
       </c>
       <c r="U28" t="n">
-        <v>3.79</v>
+        <v>4</v>
       </c>
       <c r="V28" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W28" t="n">
-        <v>3.14</v>
+        <v>2.65</v>
       </c>
       <c r="X28" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.7</v>
+        <v>6.85</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AB28" t="n">
         <v>1.02</v>
       </c>
       <c r="AC28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.26</v>
       </c>
-      <c r="AD28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AI28" t="n">
-        <v>5.35</v>
+        <v>8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.5</v>
+        <v>3.42</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.95</v>
+        <v>3.08</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.88</v>
+        <v>2.24</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.47</v>
+        <v>1.23</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46132.66666666666</v>
+        <v>46132.65625</v>
       </c>
     </row>
     <row r="29">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,134 +6120,134 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="Q29" t="n">
         <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>2.22</v>
+        <v>2.89</v>
       </c>
       <c r="S29" t="n">
-        <v>3.35</v>
+        <v>3.04</v>
       </c>
       <c r="T29" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="U29" t="n">
-        <v>2.8</v>
+        <v>3.79</v>
       </c>
       <c r="V29" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W29" t="n">
-        <v>2.73</v>
+        <v>3.15</v>
       </c>
       <c r="X29" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z29" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI29" t="n">
-        <v>6.25</v>
+        <v>5.35</v>
       </c>
       <c r="AJ29" t="n">
         <v>1.11</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AM29" t="n">
         <v>1.33</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.74</v>
+        <v>2.08</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.85</v>
+        <v>2.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>2.83</v>
+        <v>3.95</v>
       </c>
       <c r="AV29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC29" t="n">
         <v>2.1</v>
       </c>
-      <c r="AW29" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AY29" t="n">
+      <c r="BD29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BF29" t="n">
         <v>1.18</v>
       </c>
-      <c r="AZ29" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BG29" t="n">
         <v>0</v>
       </c>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46132.67708333334</v>
+        <v>46132.66666666666</v>
       </c>
     </row>
     <row r="30">
@@ -6264,27 +6264,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.11</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD30" t="n">
         <v>3.3</v>
       </c>
-      <c r="S30" t="n">
-        <v>3</v>
-      </c>
-      <c r="T30" t="n">
+      <c r="AE30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF30" t="n">
         <v>1.85</v>
       </c>
-      <c r="U30" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W30" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y30" t="n">
+      <c r="AG30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AY30" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z30" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ30" t="n">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.32</v>
+        <v>1.88</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="BC30" t="n">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="BD30" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>46132.83333333334</v>
+        <v>46132.67708333334</v>
       </c>
     </row>
     <row r="31">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,130 +6908,130 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="R33" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="S33" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="T33" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="U33" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="V33" t="n">
         <v>1.55</v>
       </c>
       <c r="W33" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X33" t="n">
-        <v>3.74</v>
+        <v>3.65</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z33" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="AE33" t="n">
         <v>2.81</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AG33" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AI33" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AJ33" t="n">
         <v>1.03</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AN33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
         <v>1.73</v>
       </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>1.63</v>
-      </c>
       <c r="BA33" t="n">
-        <v>3.68</v>
+        <v>2.32</v>
       </c>
       <c r="BB33" t="n">
         <v>1.44</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BD33" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BF33" t="n">
         <v>1.06</v>
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46132.875</v>
+        <v>46132.83333333334</v>
       </c>
     </row>
     <row r="34">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.35</v>
+        <v>2.87</v>
       </c>
       <c r="R34" t="n">
-        <v>4.01</v>
+        <v>3.9</v>
       </c>
       <c r="S34" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U34" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AR34" t="n">
         <v>2.43</v>
       </c>
-      <c r="T34" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U34" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7249,12 +7249,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,141 +7302,338 @@
         </is>
       </c>
       <c r="P35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R35" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI35" s="3" t="n">
+        <v>46132.875</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Universidad Católica</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
         <v>1.44</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Q36" t="n">
         <v>4</v>
       </c>
-      <c r="R35" t="n">
+      <c r="R36" t="n">
         <v>6.19</v>
       </c>
-      <c r="S35" t="n">
+      <c r="S36" t="n">
         <v>1.95</v>
       </c>
-      <c r="T35" t="n">
+      <c r="T36" t="n">
         <v>2.3</v>
       </c>
-      <c r="U35" t="n">
+      <c r="U36" t="n">
         <v>6.12</v>
       </c>
-      <c r="V35" t="n">
+      <c r="V36" t="n">
         <v>1.33</v>
       </c>
-      <c r="W35" t="n">
+      <c r="W36" t="n">
         <v>3.1</v>
       </c>
-      <c r="X35" t="n">
+      <c r="X36" t="n">
         <v>2.5</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="Y36" t="n">
         <v>1.43</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="Z36" t="n">
         <v>6.15</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AA36" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AB36" t="n">
         <v>1.04</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AC36" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD35" t="n">
+      <c r="AD36" t="n">
         <v>3.8</v>
       </c>
-      <c r="AE35" t="n">
+      <c r="AE36" t="n">
         <v>1.73</v>
       </c>
-      <c r="AF35" t="n">
+      <c r="AF36" t="n">
         <v>2</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AG36" t="n">
         <v>2.83</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AH36" t="n">
         <v>1.38</v>
       </c>
-      <c r="AI35" t="n">
+      <c r="AI36" t="n">
         <v>6.1</v>
       </c>
-      <c r="AJ35" t="n">
+      <c r="AJ36" t="n">
         <v>1.13</v>
       </c>
-      <c r="AK35" t="n">
+      <c r="AK36" t="n">
         <v>1.85</v>
       </c>
-      <c r="AL35" t="n">
+      <c r="AL36" t="n">
         <v>1.77</v>
       </c>
-      <c r="AM35" t="n">
+      <c r="AM36" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN35" t="n">
+      <c r="AN36" t="n">
         <v>2.5</v>
       </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
         <v>1.26</v>
       </c>
-      <c r="AQ35" t="n">
+      <c r="AQ36" t="n">
         <v>1.53</v>
       </c>
-      <c r="AR35" t="n">
+      <c r="AR36" t="n">
         <v>1.89</v>
       </c>
-      <c r="AS35" t="n">
+      <c r="AS36" t="n">
         <v>2.42</v>
       </c>
-      <c r="AT35" t="n">
+      <c r="AT36" t="n">
         <v>3.28</v>
       </c>
-      <c r="AU35" t="n">
+      <c r="AU36" t="n">
         <v>3.2</v>
       </c>
-      <c r="AV35" t="n">
+      <c r="AV36" t="n">
         <v>2.3</v>
       </c>
-      <c r="AW35" t="n">
+      <c r="AW36" t="n">
         <v>1.81</v>
       </c>
-      <c r="AX35" t="n">
+      <c r="AX36" t="n">
         <v>1.48</v>
       </c>
-      <c r="AY35" t="n">
+      <c r="AY36" t="n">
         <v>1.25</v>
       </c>
-      <c r="AZ35" t="n">
+      <c r="AZ36" t="n">
         <v>1.34</v>
       </c>
-      <c r="BA35" t="n">
+      <c r="BA36" t="n">
         <v>3.45</v>
       </c>
-      <c r="BB35" t="n">
+      <c r="BB36" t="n">
         <v>1.17</v>
       </c>
-      <c r="BC35" t="n">
+      <c r="BC36" t="n">
         <v>2.12</v>
       </c>
-      <c r="BD35" t="n">
+      <c r="BD36" t="n">
         <v>4.1</v>
       </c>
-      <c r="BE35" t="n">
+      <c r="BE36" t="n">
         <v>1.63</v>
       </c>
-      <c r="BF35" t="n">
+      <c r="BF36" t="n">
         <v>1.18</v>
       </c>
-      <c r="BG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI35" s="3" t="n">
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI36" s="3" t="n">
         <v>46132.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>1.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="R12" t="n">
-        <v>2.87</v>
+        <v>3.85</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="T12" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG12" t="n">
         <v>2.3</v>
       </c>
-      <c r="U12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.71</v>
+        <v>3.16</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.17</v>
+        <v>2.79</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="BD12" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
         <v>3.4</v>
       </c>
       <c r="V13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AY13" t="n">
         <v>1.36</v>
       </c>
-      <c r="W13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AZ13" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="BB13" t="n">
         <v>1.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.9</v>
+        <v>3.42</v>
       </c>
       <c r="R14" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="S14" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="U14" t="n">
-        <v>4.44</v>
+        <v>3.4</v>
       </c>
       <c r="V14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC14" t="n">
         <v>1.25</v>
       </c>
-      <c r="W14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AD14" t="n">
-        <v>4.75</v>
+        <v>3.54</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.3</v>
+        <v>2.76</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AI14" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BB14" t="n">
         <v>1.2</v>
       </c>
-      <c r="AK14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AM14" t="n">
+      <c r="BC14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BF14" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,22 +3756,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>1.49</v>
+        <v>8</v>
       </c>
       <c r="T17" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="U17" t="n">
-        <v>7.5</v>
+        <v>1.58</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3780,10 +3780,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -3795,40 +3795,40 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.21</v>
+        <v>1.45</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.65</v>
+        <v>2.45</v>
       </c>
       <c r="AG17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.58</v>
       </c>
-      <c r="AH17" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AI17" t="n">
-        <v>2.28</v>
+        <v>3.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AN17" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,16 +3873,16 @@
         <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>4.75</v>
+        <v>1.49</v>
       </c>
       <c r="T19" t="n">
-        <v>2.18</v>
+        <v>3.35</v>
       </c>
       <c r="U19" t="n">
-        <v>2.27</v>
+        <v>7.5</v>
       </c>
       <c r="V19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.6</v>
+        <v>1.63</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF19" t="n">
         <v>3.65</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AG19" t="n">
-        <v>2.95</v>
+        <v>1.58</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="AI19" t="n">
-        <v>5.26</v>
+        <v>2.28</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AL19" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.2</v>
+        <v>3.65</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,22 +4347,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>11.2</v>
+        <v>4.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>2.23</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4371,10 +4371,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -4386,40 +4386,40 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,13 +4464,13 @@
         <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="BF20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.34</v>
+        <v>4</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="T21" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="U21" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X21" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AD21" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AE21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BA21" t="n">
         <v>1.6</v>
       </c>
-      <c r="AF21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="R22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W22" t="n">
         <v>2.56</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U22" t="n">
+      <c r="X22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BD22" t="n">
         <v>3.4</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>3.58</v>
-      </c>
       <c r="BE22" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="R23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X23" t="n">
         <v>2.8</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U23" t="n">
-        <v>3</v>
-      </c>
-      <c r="V23" t="n">
+      <c r="Y23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN23" t="n">
         <v>1.44</v>
       </c>
-      <c r="W23" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC23" t="n">
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AY23" t="n">
         <v>1.29</v>
       </c>
-      <c r="AD23" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG23" t="n">
+      <c r="AZ23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BD23" t="n">
         <v>3.58</v>
       </c>
-      <c r="AH23" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BE23" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="R26" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="S26" t="n">
         <v>2</v>
@@ -5550,16 +5550,16 @@
         <v>1.4</v>
       </c>
       <c r="W26" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="X26" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.25</v>
+        <v>6.1</v>
       </c>
       <c r="AA26" t="n">
         <v>1.06</v>
@@ -5574,10 +5574,10 @@
         <v>3.38</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AG26" t="n">
         <v>3.05</v>
@@ -5586,10 +5586,10 @@
         <v>1.31</v>
       </c>
       <c r="AI26" t="n">
-        <v>6.82</v>
+        <v>6.75</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK26" t="n">
         <v>1.95</v>
@@ -5613,7 +5613,7 @@
         <v>1.45</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AS26" t="n">
         <v>2.12</v>
@@ -5625,10 +5625,10 @@
         <v>3.42</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AX26" t="n">
         <v>1.51</v>
@@ -5649,10 +5649,10 @@
         <v>2.2</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="BF26" t="n">
         <v>1.15</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.87</v>
+        <v>3.35</v>
       </c>
       <c r="R34" t="n">
-        <v>3.9</v>
+        <v>4.01</v>
       </c>
       <c r="S34" t="n">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="T34" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="U34" t="n">
-        <v>5.25</v>
+        <v>4.35</v>
       </c>
       <c r="V34" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="W34" t="n">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="X34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AG34" t="n">
-        <v>5.3</v>
+        <v>3.55</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AI34" t="n">
-        <v>11.5</v>
+        <v>6.75</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
         <v>1.52</v>
       </c>
-      <c r="AQ34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BF34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.35</v>
+        <v>2.87</v>
       </c>
       <c r="R35" t="n">
-        <v>4.01</v>
+        <v>3.9</v>
       </c>
       <c r="S35" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U35" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AR35" t="n">
         <v>2.43</v>
       </c>
-      <c r="T35" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U35" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>0</v>
-      </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1983,40 +1983,40 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="S8" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="T8" t="n">
         <v>2.15</v>
       </c>
       <c r="U8" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W8" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="X8" t="n">
-        <v>2.96</v>
+        <v>3.17</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB8" t="n">
         <v>1.02</v>
@@ -2025,19 +2025,19 @@
         <v>1.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG8" t="n">
         <v>3.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AI8" t="n">
         <v>7.1</v>
@@ -2049,13 +2049,13 @@
         <v>2.05</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2103,10 +2103,10 @@
         <v>2.24</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="BF8" t="n">
         <v>1.13</v>
@@ -2386,19 +2386,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="U10" t="n">
-        <v>4.28</v>
+        <v>3.9</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="X10" t="n">
         <v>2.75</v>
@@ -2407,7 +2407,7 @@
         <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.55</v>
+        <v>7</v>
       </c>
       <c r="AA10" t="n">
         <v>1.05</v>
@@ -2416,31 +2416,31 @@
         <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AH10" t="n">
         <v>1.27</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.95</v>
+        <v>5.9</v>
       </c>
       <c r="AJ10" t="n">
         <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AL10" t="n">
         <v>1.94</v>
@@ -2449,7 +2449,7 @@
         <v>1.24</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN12" t="n">
         <v>1.65</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU12" t="n">
         <v>3.9</v>
       </c>
-      <c r="R12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AJ12" t="n">
+      <c r="AV12" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BB12" t="n">
         <v>1.2</v>
       </c>
-      <c r="AK12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BC12" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="R13" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="U13" t="n">
         <v>3.4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="X13" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.55</v>
+        <v>5.95</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="AE13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR13" t="n">
         <v>1.71</v>
       </c>
-      <c r="AF13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AS13" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="BB13" t="n">
         <v>1.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BD13" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,76 +3165,76 @@
         </is>
       </c>
       <c r="P14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL14" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="R14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AM14" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AN14" t="n">
         <v>1.67</v>
@@ -3243,55 +3243,55 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.71</v>
+        <v>2.06</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.75</v>
+        <v>2.97</v>
       </c>
       <c r="AU14" t="n">
         <v>3.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BC14" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.05</v>
+        <v>4.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>2.11</v>
       </c>
       <c r="T15" t="n">
-        <v>2.05</v>
+        <v>2.47</v>
       </c>
       <c r="U15" t="n">
-        <v>3.5</v>
+        <v>4.58</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="W15" t="n">
-        <v>3</v>
+        <v>3.68</v>
       </c>
       <c r="X15" t="n">
-        <v>2.65</v>
+        <v>2.17</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.44</v>
+        <v>5.1</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AF15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE15" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG15" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.82</v>
-      </c>
       <c r="BF15" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3559,19 +3559,19 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S16" t="n">
         <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="U16" t="n">
         <v>2.9</v>
@@ -3583,13 +3583,13 @@
         <v>2.85</v>
       </c>
       <c r="X16" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="Y16" t="n">
         <v>1.41</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="AA16" t="n">
         <v>1.05</v>
@@ -3598,28 +3598,28 @@
         <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
         <v>2.92</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AI16" t="n">
-        <v>6</v>
+        <v>5.48</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK16" t="n">
         <v>1.62</v>
@@ -3637,13 +3637,13 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.38</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AS16" t="n">
         <v>2.13</v>
@@ -3658,10 +3658,10 @@
         <v>2.67</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AY16" t="n">
         <v>1.4</v>
@@ -3673,19 +3673,19 @@
         <v>2.29</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="BC16" t="n">
         <v>2</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BE16" t="n">
         <v>1.73</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>11.2</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BB17" t="n">
         <v>1.22</v>
       </c>
-      <c r="S17" t="n">
-        <v>8</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK17" t="n">
+      <c r="BC17" t="n">
         <v>1.95</v>
       </c>
-      <c r="AL17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.74</v>
+        <v>4.34</v>
       </c>
       <c r="Q18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD18" t="n">
         <v>4</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4070,13 +4070,13 @@
         <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="BF18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,22 +4150,22 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S19" t="n">
-        <v>1.49</v>
+        <v>4.7</v>
       </c>
       <c r="T19" t="n">
-        <v>3.35</v>
+        <v>2.45</v>
       </c>
       <c r="U19" t="n">
-        <v>7.5</v>
+        <v>2.05</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4174,10 +4174,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -4189,40 +4189,40 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.21</v>
+        <v>1.55</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.65</v>
+        <v>2.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.28</v>
+        <v>4.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.06</v>
+        <v>2.1</v>
       </c>
       <c r="AN19" t="n">
-        <v>3.65</v>
+        <v>1.11</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4267,16 +4267,16 @@
         <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,22 +4347,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.34</v>
+        <v>11.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.69</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="T20" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="U20" t="n">
-        <v>2.23</v>
+        <v>1.58</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4371,10 +4371,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -4386,40 +4386,40 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AD20" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AI20" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,13 +4464,13 @@
         <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="BF20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>4.75</v>
+        <v>1.49</v>
       </c>
       <c r="T21" t="n">
-        <v>2.18</v>
+        <v>3.35</v>
       </c>
       <c r="U21" t="n">
-        <v>2.27</v>
+        <v>7.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.6</v>
+        <v>1.63</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="Z21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF21" t="n">
         <v>3.65</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AG21" t="n">
-        <v>2.95</v>
+        <v>1.58</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.26</v>
+        <v>2.28</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AL21" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.2</v>
+        <v>3.65</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X22" t="n">
         <v>2.8</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3</v>
-      </c>
-      <c r="V22" t="n">
+      <c r="Y22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN22" t="n">
         <v>1.44</v>
       </c>
-      <c r="W22" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC22" t="n">
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AY22" t="n">
         <v>1.29</v>
       </c>
-      <c r="AD22" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG22" t="n">
+      <c r="AZ22" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BD22" t="n">
         <v>3.58</v>
       </c>
-      <c r="AH22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BE22" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="R23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W23" t="n">
         <v>2.56</v>
       </c>
-      <c r="S23" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="X23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BD23" t="n">
         <v>3.4</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>3.58</v>
-      </c>
       <c r="BE23" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7174,7 +7174,7 @@
         <v>1.8</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AN34" t="n">
         <v>1.74</v>
@@ -7499,37 +7499,37 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R36" t="n">
-        <v>6.19</v>
+        <v>5.5</v>
       </c>
       <c r="S36" t="n">
         <v>1.95</v>
       </c>
       <c r="T36" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U36" t="n">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="V36" t="n">
         <v>1.33</v>
       </c>
       <c r="W36" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="X36" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z36" t="n">
-        <v>6.15</v>
+        <v>6.1</v>
       </c>
       <c r="AA36" t="n">
         <v>1.06</v>
@@ -7538,16 +7538,16 @@
         <v>1.04</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AF36" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AG36" t="n">
         <v>2.83</v>
@@ -7556,7 +7556,7 @@
         <v>1.38</v>
       </c>
       <c r="AI36" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="AJ36" t="n">
         <v>1.13</v>
@@ -7568,7 +7568,7 @@
         <v>1.77</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AN36" t="n">
         <v>2.5</v>
@@ -7577,22 +7577,22 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.53</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.89</v>
+        <v>2.17</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AT36" t="n">
         <v>3.28</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AV36" t="n">
         <v>2.3</v>
@@ -7601,7 +7601,7 @@
         <v>1.81</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="AY36" t="n">
         <v>1.25</v>
@@ -7610,19 +7610,19 @@
         <v>1.34</v>
       </c>
       <c r="BA36" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="BD36" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="BF36" t="n">
         <v>1.18</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2392,7 +2392,7 @@
         <v>2.05</v>
       </c>
       <c r="U10" t="n">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="V10" t="n">
         <v>1.38</v>
@@ -2404,7 +2404,7 @@
         <v>2.75</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
         <v>7</v>
@@ -2446,7 +2446,7 @@
         <v>1.94</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AN10" t="n">
         <v>1.75</v>
@@ -2494,13 +2494,13 @@
         <v>1.25</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="BD10" t="n">
         <v>3.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="BF10" t="n">
         <v>1.17</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R12" t="n">
-        <v>2.87</v>
+        <v>4.05</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>2.11</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="U12" t="n">
-        <v>3.4</v>
+        <v>4.58</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="W12" t="n">
-        <v>3.2</v>
+        <v>3.68</v>
       </c>
       <c r="X12" t="n">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.55</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AB12" t="n">
         <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.65</v>
+        <v>2.16</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.71</v>
+        <v>3.16</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.17</v>
+        <v>2.79</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="BD12" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,76 +2968,76 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL13" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="R13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AM13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AN13" t="n">
         <v>1.67</v>
@@ -3046,55 +3046,55 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.71</v>
+        <v>2.06</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.75</v>
+        <v>2.97</v>
       </c>
       <c r="AU13" t="n">
         <v>3.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BC13" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.05</v>
+        <v>4.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,76 +3165,76 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="R14" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="U14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM14" t="n">
         <v>1.33</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.31</v>
       </c>
       <c r="AN14" t="n">
         <v>1.67</v>
@@ -3243,55 +3243,55 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.06</v>
+        <v>1.71</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="AU14" t="n">
         <v>3.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.4</v>
+        <v>4.05</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>4.05</v>
+        <v>2.87</v>
       </c>
       <c r="S15" t="n">
-        <v>2.11</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>4.58</v>
+        <v>3.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="W15" t="n">
-        <v>3.68</v>
+        <v>3.2</v>
       </c>
       <c r="X15" t="n">
-        <v>2.17</v>
+        <v>2.55</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>5</v>
+        <v>5.55</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AB15" t="n">
         <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AD15" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AI15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU15" t="n">
         <v>3.9</v>
       </c>
-      <c r="AJ15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AV15" t="n">
-        <v>3.16</v>
+        <v>2.71</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.79</v>
+        <v>2.17</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="Q17" t="n">
         <v>4</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="S17" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="T17" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="U17" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="V17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN17" t="n">
         <v>1.11</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.74</v>
+        <v>11.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="R19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.58</v>
       </c>
-      <c r="S19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T19" t="n">
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2.45</v>
       </c>
-      <c r="U19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AG19" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="AM19" t="n">
-        <v>2.1</v>
+        <v>1.08</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4267,13 +4267,13 @@
         <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="BF19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>1.49</v>
       </c>
       <c r="T20" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="U20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.58</v>
       </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AH20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.58</v>
       </c>
-      <c r="AI20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AL20" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,16 +4464,16 @@
         <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S21" t="n">
-        <v>1.49</v>
+        <v>4.75</v>
       </c>
       <c r="T21" t="n">
-        <v>3.35</v>
+        <v>2.18</v>
       </c>
       <c r="U21" t="n">
-        <v>7.5</v>
+        <v>2.27</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X21" t="n">
-        <v>1.63</v>
+        <v>2.6</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL21" t="n">
         <v>2</v>
       </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL21" t="n">
+      <c r="AM21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS21" t="n">
         <v>2.2</v>
       </c>
-      <c r="AM21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>7.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AB22" t="n">
         <v>1.06</v>
@@ -4783,13 +4783,13 @@
         <v>1.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AE22" t="n">
         <v>2.02</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG22" t="n">
         <v>3.5</v>
@@ -4801,19 +4801,19 @@
         <v>7</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4822,13 +4822,13 @@
         <v>1.22</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AR22" t="n">
         <v>1.82</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AT22" t="n">
         <v>3.06</v>
@@ -4837,7 +4837,7 @@
         <v>3.42</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.53</v>
+        <v>2.42</v>
       </c>
       <c r="AW22" t="n">
         <v>1.95</v>
@@ -4852,7 +4852,7 @@
         <v>1.93</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.39</v>
+        <v>2.19</v>
       </c>
       <c r="BB22" t="n">
         <v>1.25</v>
@@ -4861,13 +4861,13 @@
         <v>2.21</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="BE22" t="n">
         <v>1.61</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4956,7 +4956,7 @@
         <v>3</v>
       </c>
       <c r="V23" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W23" t="n">
         <v>2.56</v>
@@ -4974,40 +4974,40 @@
         <v>1.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AD23" t="n">
         <v>2.97</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG23" t="n">
         <v>3.58</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AI23" t="n">
         <v>7.5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AK23" t="n">
         <v>1.8</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AN23" t="n">
         <v>1.41</v>
@@ -5016,16 +5016,16 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="AT23" t="n">
         <v>3.42</v>
@@ -5034,22 +5034,22 @@
         <v>3.09</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AX23" t="n">
         <v>1.45</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AZ23" t="n">
         <v>1.99</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="BB23" t="n">
         <v>1.29</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.11</v>
+        <v>1.61</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.75</v>
+        <v>3.42</v>
       </c>
       <c r="R31" t="n">
-        <v>3.3</v>
+        <v>5.34</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>2.22</v>
       </c>
       <c r="T31" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="U31" t="n">
-        <v>4.2</v>
+        <v>6.19</v>
       </c>
       <c r="V31" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W31" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="X31" t="n">
-        <v>3.65</v>
+        <v>3.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="AA31" t="n">
         <v>1.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.16</v>
+        <v>2.74</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.81</v>
+        <v>2.12</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AG31" t="n">
-        <v>5.7</v>
+        <v>3.74</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AI31" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="AJ31" t="n">
         <v>1.03</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="BC31" t="n">
-        <v>3</v>
+        <v>2.27</v>
       </c>
       <c r="BD31" t="n">
-        <v>2.5</v>
+        <v>3.28</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6825,19 +6825,19 @@
         <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7314,19 +7314,19 @@
         <v>2.66</v>
       </c>
       <c r="T35" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="U35" t="n">
         <v>5.25</v>
       </c>
       <c r="V35" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="W35" t="n">
         <v>2.23</v>
       </c>
       <c r="X35" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Y35" t="n">
         <v>1.19</v>
@@ -7341,16 +7341,16 @@
         <v>1.08</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AD35" t="n">
         <v>2.25</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AG35" t="n">
         <v>5.3</v>
@@ -7380,16 +7380,16 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AR35" t="n">
         <v>2.43</v>
       </c>
       <c r="AS35" t="n">
-        <v>3.15</v>
+        <v>3.57</v>
       </c>
       <c r="AT35" t="n">
         <v>5.41</v>
@@ -7416,10 +7416,10 @@
         <v>3.22</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="BD35" t="n">
         <v>2.63</v>
@@ -7428,7 +7428,7 @@
         <v>1.36</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI36"/>
+  <dimension ref="A1:BI38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="Q2" t="n">
         <v>3.3</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="S2" t="n">
         <v>2.75</v>
@@ -816,7 +816,7 @@
         <v>2.2</v>
       </c>
       <c r="U2" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="V2" t="n">
         <v>1.33</v>
@@ -825,7 +825,7 @@
         <v>2.88</v>
       </c>
       <c r="X2" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="Y2" t="n">
         <v>1.36</v>
@@ -837,13 +837,13 @@
         <v>1.04</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC2" t="n">
         <v>1.24</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AE2" t="n">
         <v>1.87</v>
@@ -882,13 +882,13 @@
         <v>1.24</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AR2" t="n">
         <v>2.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="AT2" t="n">
         <v>3.15</v>
@@ -897,13 +897,13 @@
         <v>3.32</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="AW2" t="n">
         <v>1.85</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AY2" t="n">
         <v>1.27</v>
@@ -912,7 +912,7 @@
         <v>1.56</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.32</v>
+        <v>2.75</v>
       </c>
       <c r="BB2" t="n">
         <v>1.18</v>
@@ -921,13 +921,13 @@
         <v>2.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1395,7 +1395,7 @@
         <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
         <v>2.17</v>
@@ -1404,7 +1404,7 @@
         <v>3.61</v>
       </c>
       <c r="T5" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
         <v>2.63</v>
@@ -1416,7 +1416,7 @@
         <v>2.86</v>
       </c>
       <c r="X5" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Y5" t="n">
         <v>1.43</v>
@@ -1437,13 +1437,13 @@
         <v>3.68</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="AH5" t="n">
         <v>1.36</v>
@@ -1452,7 +1452,7 @@
         <v>4.85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AK5" t="n">
         <v>1.62</v>
@@ -1509,16 +1509,16 @@
         <v>1.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -2180,19 +2180,19 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="R9" t="n">
-        <v>7.1</v>
+        <v>7.43</v>
       </c>
       <c r="S9" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="T9" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="U9" t="n">
         <v>7</v>
@@ -2216,7 +2216,7 @@
         <v>1.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC9" t="n">
         <v>1.23</v>
@@ -2225,10 +2225,10 @@
         <v>3.84</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
         <v>2.56</v>
@@ -2249,10 +2249,10 @@
         <v>1.8</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2264,46 +2264,46 @@
         <v>1.45</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
       <c r="AX9" t="n">
         <v>1.58</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AZ9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="BB9" t="n">
         <v>1.22</v>
       </c>
-      <c r="BA9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC9" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="BF9" t="n">
         <v>1.2</v>
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="R11" t="n">
-        <v>4.73</v>
+        <v>4.65</v>
       </c>
       <c r="S11" t="n">
         <v>1.98</v>
@@ -2604,19 +2604,19 @@
         <v>1.48</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
         <v>1.16</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AE11" t="n">
         <v>1.66</v>
@@ -2664,7 +2664,7 @@
         <v>1.97</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.37</v>
+        <v>2.52</v>
       </c>
       <c r="AU11" t="n">
         <v>4.3</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="R12" t="n">
-        <v>4.05</v>
+        <v>2.83</v>
       </c>
       <c r="S12" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>4.58</v>
+        <v>3.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>3.68</v>
+        <v>3.23</v>
       </c>
       <c r="X12" t="n">
-        <v>2.17</v>
+        <v>2.55</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>5.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AB12" t="n">
         <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AD12" t="n">
-        <v>5.1</v>
+        <v>3.82</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AI12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU12" t="n">
         <v>3.9</v>
       </c>
-      <c r="AJ12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AV12" t="n">
-        <v>3.16</v>
+        <v>2.71</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.79</v>
+        <v>2.28</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="R13" t="n">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>2.11</v>
       </c>
       <c r="T13" t="n">
-        <v>2.05</v>
+        <v>2.47</v>
       </c>
       <c r="U13" t="n">
-        <v>3.5</v>
+        <v>4.58</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="W13" t="n">
-        <v>3</v>
+        <v>3.68</v>
       </c>
       <c r="X13" t="n">
-        <v>2.65</v>
+        <v>2.17</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.44</v>
+        <v>5.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AF13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE13" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG13" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.82</v>
-      </c>
       <c r="BF13" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3168,7 +3168,7 @@
         <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
         <v>3.1</v>
@@ -3177,7 +3177,7 @@
         <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="U14" t="n">
         <v>3.4</v>
@@ -3186,10 +3186,10 @@
         <v>1.36</v>
       </c>
       <c r="W14" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="X14" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="Y14" t="n">
         <v>1.44</v>
@@ -3201,7 +3201,7 @@
         <v>1.07</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC14" t="n">
         <v>1.25</v>
@@ -3213,16 +3213,16 @@
         <v>1.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AG14" t="n">
         <v>2.76</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AI14" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AJ14" t="n">
         <v>1.1</v>
@@ -3231,7 +3231,7 @@
         <v>1.67</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AM14" t="n">
         <v>1.33</v>
@@ -3243,13 +3243,13 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.71</v>
+        <v>2.26</v>
       </c>
       <c r="AS14" t="n">
         <v>2.14</v>
@@ -3261,13 +3261,13 @@
         <v>3.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.63</v>
+        <v>2.34</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="AY14" t="n">
         <v>1.38</v>
@@ -3276,7 +3276,7 @@
         <v>1.8</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BB14" t="n">
         <v>1.2</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.12</v>
+        <v>2.37</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
-        <v>2.87</v>
+        <v>2.58</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>3.02</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W15" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="X15" t="n">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="Z15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI15" t="n">
         <v>5.55</v>
       </c>
-      <c r="AA15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>4.75</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AR15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX15" t="n">
         <v>1.67</v>
       </c>
-      <c r="AS15" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AY15" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="BB15" t="n">
         <v>1.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3506,27 +3506,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,64 +3559,64 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.57</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.52</v>
+        <v>3.35</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="T16" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="U16" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="X16" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Z16" t="n">
         <v>6</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.05</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1</v>
-      </c>
       <c r="AC16" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AF16" t="n">
         <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="AH16" t="n">
         <v>1.33</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.48</v>
+        <v>5.1</v>
       </c>
       <c r="AJ16" t="n">
         <v>1.13</v>
@@ -3628,64 +3628,64 @@
         <v>2.15</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AR16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW16" t="n">
         <v>1.91</v>
       </c>
-      <c r="AS16" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AX16" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="BB16" t="n">
         <v>1.22</v>
       </c>
       <c r="BC16" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BE16" t="n">
         <v>1.73</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46132.58680555555</v>
+        <v>46132.58333333334</v>
       </c>
     </row>
     <row r="17">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.74</v>
+        <v>2.57</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.58</v>
+        <v>2.52</v>
       </c>
       <c r="S17" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="U17" t="n">
-        <v>2.05</v>
+        <v>2.9</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X17" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.38</v>
+        <v>2.92</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.1</v>
+        <v>5.48</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK17" t="n">
         <v>1.62</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AM17" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.11</v>
+        <v>1.44</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46132.60416666666</v>
+        <v>46132.58680555555</v>
       </c>
     </row>
     <row r="18">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.34</v>
+        <v>4.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="S18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD18" t="n">
         <v>4.2</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AM18" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AN18" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4070,13 +4070,13 @@
         <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="BF18" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD21" t="n">
         <v>4</v>
       </c>
-      <c r="Q21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.65</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.95</v>
+        <v>2.48</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.26</v>
+        <v>4.3</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AL21" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4688,12 +4688,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>2.56</v>
+        <v>1.72</v>
       </c>
       <c r="S22" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT22" t="n">
         <v>2.85</v>
       </c>
-      <c r="T22" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
+      <c r="AU22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BB22" t="n">
         <v>1.22</v>
       </c>
-      <c r="AQ22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC22" t="n">
-        <v>2.21</v>
+        <v>1.94</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46132.61458333334</v>
+        <v>46132.60416666666</v>
       </c>
     </row>
     <row r="23">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46132.625</v>
+        <v>46132.61458333334</v>
       </c>
     </row>
     <row r="25">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="R26" t="n">
-        <v>5.5</v>
+        <v>3.87</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="T26" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="U26" t="n">
-        <v>5.75</v>
+        <v>3.5</v>
       </c>
       <c r="V26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AZ26" t="n">
         <v>1.4</v>
       </c>
-      <c r="W26" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BA26" t="n">
-        <v>3.85</v>
+        <v>2.38</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.2</v>
+        <v>1.64</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.88</v>
+        <v>5</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46132.64583333334</v>
+        <v>46132.625</v>
       </c>
     </row>
     <row r="27">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="R27" t="n">
-        <v>2.12</v>
+        <v>5.5</v>
       </c>
       <c r="S27" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U27" t="n">
-        <v>2.63</v>
+        <v>5.75</v>
       </c>
       <c r="V27" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W27" t="n">
-        <v>2.68</v>
+        <v>3.02</v>
       </c>
       <c r="X27" t="n">
-        <v>3.21</v>
+        <v>2.65</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="Z27" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="AA27" t="n">
         <v>1.06</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.86</v>
+        <v>3.05</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AI27" t="n">
-        <v>8</v>
+        <v>6.75</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.3</v>
+        <v>2.45</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AY27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB27" t="n">
         <v>1.29</v>
       </c>
-      <c r="AZ27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.27</v>
-      </c>
       <c r="BC27" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.55</v>
+        <v>3.88</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46132.65625</v>
+        <v>46132.64583333334</v>
       </c>
     </row>
     <row r="28">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="Q28" t="n">
         <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="S28" t="n">
         <v>2.45</v>
@@ -5941,13 +5941,13 @@
         <v>4</v>
       </c>
       <c r="V28" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W28" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="X28" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="Y28" t="n">
         <v>1.36</v>
@@ -5971,16 +5971,16 @@
         <v>2</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.9</v>
+        <v>3.24</v>
       </c>
       <c r="AH28" t="n">
         <v>1.26</v>
       </c>
       <c r="AI28" t="n">
-        <v>8</v>
+        <v>6.15</v>
       </c>
       <c r="AJ28" t="n">
         <v>1.06</v>
@@ -6001,16 +6001,16 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AT28" t="n">
         <v>3.42</v>
@@ -6028,7 +6028,7 @@
         <v>1.43</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AZ28" t="n">
         <v>1.69</v>
@@ -6043,13 +6043,13 @@
         <v>2.16</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.36</v>
+        <v>3.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R29" t="n">
-        <v>2.89</v>
+        <v>2.15</v>
       </c>
       <c r="S29" t="n">
-        <v>3.04</v>
+        <v>3.7</v>
       </c>
       <c r="T29" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="U29" t="n">
-        <v>3.79</v>
+        <v>2.63</v>
       </c>
       <c r="V29" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="W29" t="n">
-        <v>3.15</v>
+        <v>2.68</v>
       </c>
       <c r="X29" t="n">
-        <v>2.5</v>
+        <v>3.21</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AK29" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AM29" t="n">
         <v>1.33</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.95</v>
+        <v>3.05</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.88</v>
+        <v>2.36</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.6</v>
+        <v>1.89</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46132.66666666666</v>
+        <v>46132.65625</v>
       </c>
     </row>
     <row r="30">
@@ -6264,12 +6264,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,134 +6317,134 @@
         </is>
       </c>
       <c r="P30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R30" t="n">
         <v>3</v>
       </c>
-      <c r="Q30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T30" t="n">
         <v>2.3</v>
       </c>
-      <c r="S30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.26</v>
-      </c>
       <c r="U30" t="n">
-        <v>2.8</v>
+        <v>3.81</v>
       </c>
       <c r="V30" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W30" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="X30" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z30" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA30" t="n">
         <v>1.08</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AF30" t="n">
         <v>1.85</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI30" t="n">
-        <v>6.25</v>
+        <v>5.35</v>
       </c>
       <c r="AJ30" t="n">
         <v>1.11</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.63</v>
+        <v>1.97</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.85</v>
+        <v>2.5</v>
       </c>
       <c r="AU30" t="n">
-        <v>2.83</v>
+        <v>3.95</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.1</v>
+        <v>2.74</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.72</v>
+        <v>2.17</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="AY30" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BF30" t="n">
         <v>1.18</v>
       </c>
-      <c r="AZ30" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BG30" t="n">
         <v>0</v>
       </c>
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>46132.67708333334</v>
+        <v>46132.66666666666</v>
       </c>
     </row>
     <row r="31">
@@ -6461,27 +6461,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.61</v>
+        <v>3.09</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="R31" t="n">
-        <v>5.34</v>
+        <v>2.35</v>
       </c>
       <c r="S31" t="n">
-        <v>2.22</v>
+        <v>3.35</v>
       </c>
       <c r="T31" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="U31" t="n">
-        <v>6.19</v>
+        <v>2.89</v>
       </c>
       <c r="V31" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W31" t="n">
-        <v>2.47</v>
+        <v>3.07</v>
       </c>
       <c r="X31" t="n">
-        <v>3.04</v>
+        <v>2.73</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN31" t="n">
         <v>1.35</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS31" t="n">
         <v>2.74</v>
       </c>
-      <c r="AE31" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>46132.83333333334</v>
+        <v>46132.67708333334</v>
       </c>
     </row>
     <row r="32">
@@ -6658,27 +6658,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6825,19 +6825,19 @@
         <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46132.83333333334</v>
+        <v>46132.75</v>
       </c>
     </row>
     <row r="33">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.8</v>
+        <v>3.42</v>
       </c>
       <c r="R33" t="n">
-        <v>3.4</v>
+        <v>5.34</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>2.22</v>
       </c>
       <c r="T33" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="U33" t="n">
-        <v>4.2</v>
+        <v>6.19</v>
       </c>
       <c r="V33" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W33" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="X33" t="n">
-        <v>3.65</v>
+        <v>3.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z33" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AA33" t="n">
         <v>1.03</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.21</v>
+        <v>2.74</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.78</v>
+        <v>2.12</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="AG33" t="n">
-        <v>5.6</v>
+        <v>3.74</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AI33" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="AJ33" t="n">
         <v>1.03</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="BC33" t="n">
-        <v>3</v>
+        <v>2.27</v>
       </c>
       <c r="BD33" t="n">
-        <v>2.5</v>
+        <v>3.28</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7052,12 +7052,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="R34" t="n">
-        <v>4.01</v>
+        <v>3.4</v>
       </c>
       <c r="S34" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="U34" t="n">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="V34" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="W34" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.95</v>
+        <v>2.21</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.02</v>
+        <v>2.78</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.55</v>
+        <v>5.6</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AI34" t="n">
-        <v>6.75</v>
+        <v>13</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AM34" t="n">
         <v>1.24</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
-        <v>46132.875</v>
+        <v>46132.83333333334</v>
       </c>
     </row>
     <row r="35">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,134 +7302,134 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.95</v>
+        <v>2.52</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.87</v>
+        <v>2.44</v>
       </c>
       <c r="R35" t="n">
-        <v>3.9</v>
+        <v>3.41</v>
       </c>
       <c r="S35" t="n">
-        <v>2.66</v>
+        <v>3.44</v>
       </c>
       <c r="T35" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="U35" t="n">
-        <v>5.25</v>
+        <v>4.59</v>
       </c>
       <c r="V35" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W35" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="X35" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z35" t="n">
-        <v>12</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AG35" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="AH35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF35" t="n">
         <v>1.09</v>
       </c>
-      <c r="AI35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>1.06</v>
-      </c>
       <c r="BG35" t="n">
         <v>0</v>
       </c>
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46132.875</v>
+        <v>46132.83333333334</v>
       </c>
     </row>
     <row r="36">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,141 +7499,535 @@
         </is>
       </c>
       <c r="P36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="R36" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U36" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI36" s="3" t="n">
+        <v>46132.875</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Deportes Temuco</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R37" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI37" s="3" t="n">
+        <v>46132.875</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Universidad Católica</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
         <v>1.45</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="Q38" t="n">
         <v>3.8</v>
       </c>
-      <c r="R36" t="n">
+      <c r="R38" t="n">
         <v>5.5</v>
       </c>
-      <c r="S36" t="n">
+      <c r="S38" t="n">
         <v>1.95</v>
       </c>
-      <c r="T36" t="n">
+      <c r="T38" t="n">
         <v>2.25</v>
       </c>
-      <c r="U36" t="n">
+      <c r="U38" t="n">
         <v>6</v>
       </c>
-      <c r="V36" t="n">
+      <c r="V38" t="n">
         <v>1.33</v>
       </c>
-      <c r="W36" t="n">
+      <c r="W38" t="n">
         <v>3.05</v>
       </c>
-      <c r="X36" t="n">
+      <c r="X38" t="n">
         <v>2.66</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="Y38" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="Z38" t="n">
         <v>6.1</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AA38" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AB38" t="n">
         <v>1.04</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AC38" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AD38" t="n">
         <v>3.68</v>
       </c>
-      <c r="AE36" t="n">
+      <c r="AE38" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF36" t="n">
+      <c r="AF38" t="n">
         <v>1.94</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AG38" t="n">
         <v>2.83</v>
       </c>
-      <c r="AH36" t="n">
+      <c r="AH38" t="n">
         <v>1.38</v>
       </c>
-      <c r="AI36" t="n">
+      <c r="AI38" t="n">
         <v>5</v>
       </c>
-      <c r="AJ36" t="n">
+      <c r="AJ38" t="n">
         <v>1.13</v>
       </c>
-      <c r="AK36" t="n">
+      <c r="AK38" t="n">
         <v>1.85</v>
       </c>
-      <c r="AL36" t="n">
+      <c r="AL38" t="n">
         <v>1.77</v>
       </c>
-      <c r="AM36" t="n">
+      <c r="AM38" t="n">
         <v>1.15</v>
       </c>
-      <c r="AN36" t="n">
+      <c r="AN38" t="n">
         <v>2.5</v>
       </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
         <v>1.24</v>
       </c>
-      <c r="AQ36" t="n">
+      <c r="AQ38" t="n">
         <v>1.53</v>
       </c>
-      <c r="AR36" t="n">
+      <c r="AR38" t="n">
         <v>2.17</v>
       </c>
-      <c r="AS36" t="n">
+      <c r="AS38" t="n">
         <v>2.38</v>
       </c>
-      <c r="AT36" t="n">
+      <c r="AT38" t="n">
         <v>3.28</v>
       </c>
-      <c r="AU36" t="n">
+      <c r="AU38" t="n">
         <v>3.35</v>
       </c>
-      <c r="AV36" t="n">
+      <c r="AV38" t="n">
         <v>2.3</v>
       </c>
-      <c r="AW36" t="n">
+      <c r="AW38" t="n">
         <v>1.81</v>
       </c>
-      <c r="AX36" t="n">
+      <c r="AX38" t="n">
         <v>1.56</v>
       </c>
-      <c r="AY36" t="n">
+      <c r="AY38" t="n">
         <v>1.25</v>
       </c>
-      <c r="AZ36" t="n">
+      <c r="AZ38" t="n">
         <v>1.34</v>
       </c>
-      <c r="BA36" t="n">
+      <c r="BA38" t="n">
         <v>3.6</v>
       </c>
-      <c r="BB36" t="n">
+      <c r="BB38" t="n">
         <v>1.22</v>
       </c>
-      <c r="BC36" t="n">
+      <c r="BC38" t="n">
         <v>1.98</v>
       </c>
-      <c r="BD36" t="n">
+      <c r="BD38" t="n">
         <v>3.8</v>
       </c>
-      <c r="BE36" t="n">
+      <c r="BE38" t="n">
         <v>1.76</v>
       </c>
-      <c r="BF36" t="n">
+      <c r="BF38" t="n">
         <v>1.18</v>
       </c>
-      <c r="BG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI36" s="3" t="n">
+      <c r="BG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI38" s="3" t="n">
         <v>46132.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2007,10 +2007,10 @@
         <v>2.56</v>
       </c>
       <c r="X8" t="n">
-        <v>3.17</v>
+        <v>3.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z8" t="n">
         <v>7.7</v>
@@ -2025,13 +2025,13 @@
         <v>1.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="AE8" t="n">
         <v>2.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG8" t="n">
         <v>3.8</v>
@@ -2052,10 +2052,10 @@
         <v>1.68</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL12" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q12" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W12" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AM12" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AR12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX12" t="n">
         <v>1.67</v>
       </c>
-      <c r="AS12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AY12" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="BB12" t="n">
         <v>1.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BD12" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="R13" t="n">
-        <v>4.05</v>
+        <v>2.83</v>
       </c>
       <c r="S13" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>4.58</v>
+        <v>3.4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>3.68</v>
+        <v>3.23</v>
       </c>
       <c r="X13" t="n">
-        <v>2.17</v>
+        <v>2.55</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>5.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AB13" t="n">
         <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AD13" t="n">
-        <v>5.1</v>
+        <v>3.82</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AI13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU13" t="n">
         <v>3.9</v>
       </c>
-      <c r="AJ13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AV13" t="n">
-        <v>3.16</v>
+        <v>2.71</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.79</v>
+        <v>2.28</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R14" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="T14" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG14" t="n">
         <v>2.3</v>
       </c>
-      <c r="U14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC14" t="n">
+      <c r="AH14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BF14" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,130 +3362,130 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>2.58</v>
+        <v>3.1</v>
       </c>
       <c r="S15" t="n">
-        <v>3.02</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="X15" t="n">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.4</v>
+        <v>5.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AB15" t="n">
         <v>1.04</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.96</v>
+        <v>3.54</v>
       </c>
       <c r="AE15" t="n">
         <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="AH15" t="n">
         <v>1.39</v>
       </c>
       <c r="AI15" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AN15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>1.49</v>
       </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AR15" t="n">
-        <v>1.85</v>
+        <v>2.26</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="BB15" t="n">
         <v>1.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.96</v>
+        <v>4.05</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="BF15" t="n">
         <v>1.2</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.74</v>
+        <v>4.34</v>
       </c>
       <c r="Q18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD18" t="n">
         <v>4</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AM18" t="n">
-        <v>2.1</v>
+        <v>1.19</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4070,13 +4070,13 @@
         <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="BF18" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S20" t="n">
-        <v>1.49</v>
+        <v>4.75</v>
       </c>
       <c r="T20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU20" t="n">
         <v>3.35</v>
       </c>
-      <c r="U20" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,22 +4544,22 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2</v>
+        <v>1.49</v>
       </c>
       <c r="T21" t="n">
-        <v>2.35</v>
+        <v>3.35</v>
       </c>
       <c r="U21" t="n">
-        <v>2.23</v>
+        <v>7.5</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4568,55 +4568,55 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI21" t="n">
         <v>2.28</v>
       </c>
-      <c r="Y21" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.15</v>
+        <v>3.65</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4661,16 +4661,16 @@
         <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
         <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.8</v>
+        <v>4.74</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="S22" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="T22" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="U22" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="V22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="Z22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN22" t="n">
         <v>1.11</v>
       </c>
-      <c r="AB22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="BD22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="R23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X23" t="n">
         <v>2.8</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U23" t="n">
-        <v>3</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.95</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z23" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AI23" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AM23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BB23" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN23" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC23" t="n">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="R24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W24" t="n">
         <v>2.56</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="X24" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BD24" t="n">
         <v>3.4</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BE24" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.2</v>
+        <v>2.52</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="R34" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="T34" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="U34" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AG34" t="n">
         <v>4.2</v>
       </c>
-      <c r="V34" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W34" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AI34" t="n">
-        <v>13</v>
+        <v>8.1</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="BC34" t="n">
-        <v>3</v>
+        <v>2.41</v>
       </c>
       <c r="BD34" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="R35" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="S35" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="U35" t="n">
-        <v>4.59</v>
+        <v>4.2</v>
       </c>
       <c r="V35" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W35" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="X35" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z35" t="n">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.44</v>
+        <v>2.21</v>
       </c>
       <c r="AE35" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
         <v>2.38</v>
       </c>
-      <c r="AF35" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0</v>
-      </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE35" t="n">
         <v>1.33</v>
       </c>
-      <c r="BC35" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>1.46</v>
-      </c>
       <c r="BF35" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.87</v>
+        <v>3.35</v>
       </c>
       <c r="R36" t="n">
-        <v>3.9</v>
+        <v>4.01</v>
       </c>
       <c r="S36" t="n">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="T36" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL36" t="n">
         <v>1.8</v>
       </c>
-      <c r="U36" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="V36" t="n">
+      <c r="AM36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
         <v>1.52</v>
       </c>
-      <c r="W36" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="X36" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BF36" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.35</v>
+        <v>2.87</v>
       </c>
       <c r="R37" t="n">
-        <v>4.01</v>
+        <v>3.9</v>
       </c>
       <c r="S37" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U37" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="X37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR37" t="n">
         <v>2.43</v>
       </c>
-      <c r="T37" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U37" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W37" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ37" t="n">
+      <c r="AS37" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BF37" t="n">
         <v>1.06</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>0</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="S2" t="n">
         <v>2.75</v>
@@ -816,7 +816,7 @@
         <v>2.2</v>
       </c>
       <c r="U2" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="V2" t="n">
         <v>1.33</v>
@@ -843,34 +843,34 @@
         <v>1.24</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG2" t="n">
         <v>3.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.3</v>
+        <v>6.01</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AL2" t="n">
         <v>2</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AN2" t="n">
         <v>1.55</v>
@@ -879,40 +879,40 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.32</v>
+        <v>3.47</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="BB2" t="n">
         <v>1.18</v>
@@ -921,13 +921,13 @@
         <v>2.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1404,10 +1404,10 @@
         <v>3.61</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="U5" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="V5" t="n">
         <v>1.33</v>
@@ -1416,10 +1416,10 @@
         <v>2.86</v>
       </c>
       <c r="X5" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="Z5" t="n">
         <v>5.75</v>
@@ -1434,13 +1434,13 @@
         <v>1.22</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.68</v>
+        <v>3.99</v>
       </c>
       <c r="AE5" t="n">
         <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG5" t="n">
         <v>3.15</v>
@@ -1449,10 +1449,10 @@
         <v>1.36</v>
       </c>
       <c r="AI5" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK5" t="n">
         <v>1.62</v>
@@ -1461,61 +1461,61 @@
         <v>2.15</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AZ5" t="n">
         <v>2.09</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="BB5" t="n">
         <v>1.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BF5" t="n">
         <v>1.2</v>
@@ -1995,7 +1995,7 @@
         <v>2.15</v>
       </c>
       <c r="T8" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="U8" t="n">
         <v>5.5</v>
@@ -2004,7 +2004,7 @@
         <v>1.42</v>
       </c>
       <c r="W8" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="X8" t="n">
         <v>3.02</v>
@@ -2022,7 +2022,7 @@
         <v>1.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AD8" t="n">
         <v>3.07</v>
@@ -2037,19 +2037,19 @@
         <v>3.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AI8" t="n">
         <v>7.1</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AK8" t="n">
         <v>2.05</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AM8" t="n">
         <v>1.19</v>
@@ -2100,13 +2100,13 @@
         <v>1.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="BD8" t="n">
         <v>3.34</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="BF8" t="n">
         <v>1.13</v>
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>7.43</v>
+        <v>6</v>
       </c>
       <c r="S9" t="n">
         <v>1.8</v>
@@ -2204,10 +2204,10 @@
         <v>3.1</v>
       </c>
       <c r="X9" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="Z9" t="n">
         <v>5.6</v>
@@ -2249,7 +2249,7 @@
         <v>1.8</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="AN9" t="n">
         <v>2.75</v>
@@ -2267,13 +2267,13 @@
         <v>1.9</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="AV9" t="n">
         <v>2.63</v>
@@ -2282,7 +2282,7 @@
         <v>2.09</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AY9" t="n">
         <v>1.36</v>
@@ -2297,13 +2297,13 @@
         <v>1.22</v>
       </c>
       <c r="BC9" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="BD9" t="n">
         <v>3.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="BF9" t="n">
         <v>1.2</v>
@@ -2586,10 +2586,10 @@
         <v>1.98</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="U11" t="n">
-        <v>4.8</v>
+        <v>5.19</v>
       </c>
       <c r="V11" t="n">
         <v>1.27</v>
@@ -2619,10 +2619,10 @@
         <v>4.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AG11" t="n">
         <v>2.59</v>
@@ -2631,10 +2631,10 @@
         <v>1.4</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK11" t="n">
         <v>1.65</v>
@@ -2646,7 +2646,7 @@
         <v>1.17</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2655,13 +2655,13 @@
         <v>1.13</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AR11" t="n">
         <v>1.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AT11" t="n">
         <v>2.52</v>
@@ -2670,16 +2670,16 @@
         <v>4.3</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AX11" t="n">
         <v>1.74</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AZ11" t="n">
         <v>1.35</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.37</v>
+        <v>2.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="S12" t="n">
-        <v>3.02</v>
+        <v>2.55</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W12" t="n">
-        <v>3.21</v>
+        <v>2.77</v>
       </c>
       <c r="X12" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AA12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.05</v>
       </c>
-      <c r="AB12" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AC12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.96</v>
+        <v>3.52</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.55</v>
+        <v>5.1</v>
       </c>
       <c r="AJ12" t="n">
         <v>1.13</v>
       </c>
       <c r="AK12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN12" t="n">
         <v>1.68</v>
       </c>
-      <c r="AL12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM12" t="n">
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>1.43</v>
       </c>
-      <c r="AN12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AR12" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.4</v>
+        <v>2.97</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.23</v>
+        <v>2.49</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.3</v>
-      </c>
       <c r="U13" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W13" t="n">
-        <v>3.23</v>
+        <v>2.95</v>
       </c>
       <c r="X13" t="n">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="Z13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI13" t="n">
         <v>5.55</v>
       </c>
-      <c r="AA13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>5</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AR13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AX13" t="n">
         <v>1.67</v>
       </c>
-      <c r="AS13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AY13" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="BB13" t="n">
         <v>1.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BD13" t="n">
         <v>4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD14" t="n">
         <v>4.05</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U14" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BE14" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,130 +3362,130 @@
         </is>
       </c>
       <c r="P15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AL15" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V15" t="n">
+      <c r="AM15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY15" t="n">
         <v>1.36</v>
       </c>
-      <c r="W15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AZ15" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="BB15" t="n">
         <v>1.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="BF15" t="n">
         <v>1.2</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="S16" t="n">
-        <v>2.55</v>
+        <v>2.11</v>
       </c>
       <c r="T16" t="n">
-        <v>2.06</v>
+        <v>2.47</v>
       </c>
       <c r="U16" t="n">
-        <v>3.5</v>
+        <v>4.58</v>
       </c>
       <c r="V16" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="W16" t="n">
-        <v>2.77</v>
+        <v>3.78</v>
       </c>
       <c r="X16" t="n">
-        <v>2.62</v>
+        <v>2.17</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="Z16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.52</v>
+        <v>5.1</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AF16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE16" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BF16" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="Q17" t="n">
         <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="S17" t="n">
         <v>3.25</v>
@@ -3783,7 +3783,7 @@
         <v>2.66</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Z17" t="n">
         <v>6</v>
@@ -3795,7 +3795,7 @@
         <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AD17" t="n">
         <v>3.6</v>
@@ -3804,19 +3804,19 @@
         <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG17" t="n">
         <v>2.92</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AI17" t="n">
         <v>5.48</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK17" t="n">
         <v>1.62</v>
@@ -3834,40 +3834,40 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.84</v>
+        <v>3.55</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.67</v>
+        <v>2.53</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AY17" t="n">
         <v>1.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.29</v>
+        <v>2.05</v>
       </c>
       <c r="BB17" t="n">
         <v>1.22</v>
@@ -3879,7 +3879,7 @@
         <v>3.9</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="BF17" t="n">
         <v>1.2</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,22 +4150,22 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>11.2</v>
+        <v>4.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>4.7</v>
       </c>
       <c r="T19" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="U19" t="n">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4174,55 +4174,55 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK19" t="n">
         <v>1.62</v>
       </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG19" t="n">
+      <c r="AL19" t="n">
         <v>2.12</v>
       </c>
-      <c r="AH19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AM19" t="n">
-        <v>1.08</v>
+        <v>2.1</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4267,13 +4267,13 @@
         <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="BF19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.8</v>
+        <v>11.2</v>
       </c>
       <c r="Q20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S20" t="n">
+        <v>8</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI20" t="n">
         <v>3.5</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC20" t="n">
+      <c r="AJ20" t="n">
         <v>1.23</v>
       </c>
-      <c r="AD20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE20" t="n">
+      <c r="AK20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL20" t="n">
         <v>1.75</v>
       </c>
-      <c r="AF20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2</v>
-      </c>
       <c r="AM20" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="BD20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S21" t="n">
-        <v>1.49</v>
+        <v>4.6</v>
       </c>
       <c r="T21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU21" t="n">
         <v>3.35</v>
       </c>
-      <c r="U21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.58</v>
       </c>
-      <c r="S22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
+      <c r="AH22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL22" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AM22" t="n">
-        <v>2.1</v>
+        <v>1.06</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.11</v>
+        <v>3.65</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4858,16 +4858,16 @@
         <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4947,25 +4947,25 @@
         <v>2.56</v>
       </c>
       <c r="S23" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="U23" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="V23" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W23" t="n">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="X23" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z23" t="n">
         <v>7.2</v>
@@ -5007,10 +5007,10 @@
         <v>1.95</v>
       </c>
       <c r="AM23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN23" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.47</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5019,28 +5019,28 @@
         <v>1.22</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AR23" t="n">
         <v>1.82</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AT23" t="n">
         <v>3.06</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.42</v>
+        <v>2.53</v>
       </c>
       <c r="AW23" t="n">
         <v>1.95</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AY23" t="n">
         <v>1.29</v>
@@ -5058,13 +5058,13 @@
         <v>2.21</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5147,22 +5147,22 @@
         <v>3.44</v>
       </c>
       <c r="T24" t="n">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="U24" t="n">
         <v>3</v>
       </c>
       <c r="V24" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W24" t="n">
         <v>2.56</v>
       </c>
       <c r="X24" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
         <v>8.199999999999999</v>
@@ -5177,7 +5177,7 @@
         <v>1.38</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AE24" t="n">
         <v>2.09</v>
@@ -5186,7 +5186,7 @@
         <v>1.68</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.58</v>
+        <v>3.83</v>
       </c>
       <c r="AH24" t="n">
         <v>1.24</v>
@@ -5204,7 +5204,7 @@
         <v>1.94</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AN24" t="n">
         <v>1.41</v>
@@ -5222,7 +5222,7 @@
         <v>2.18</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="AT24" t="n">
         <v>3.42</v>
@@ -5231,10 +5231,10 @@
         <v>3.09</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AX24" t="n">
         <v>1.45</v>
@@ -5252,7 +5252,7 @@
         <v>1.29</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BD24" t="n">
         <v>3.4</v>
@@ -5935,7 +5935,7 @@
         <v>2.45</v>
       </c>
       <c r="T28" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="U28" t="n">
         <v>4</v>
@@ -5947,13 +5947,13 @@
         <v>2.62</v>
       </c>
       <c r="X28" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Y28" t="n">
         <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.85</v>
+        <v>6.8</v>
       </c>
       <c r="AA28" t="n">
         <v>1.04</v>
@@ -5971,7 +5971,7 @@
         <v>2</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG28" t="n">
         <v>3.24</v>
@@ -5980,31 +5980,31 @@
         <v>1.26</v>
       </c>
       <c r="AI28" t="n">
-        <v>6.15</v>
+        <v>6.05</v>
       </c>
       <c r="AJ28" t="n">
         <v>1.06</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL28" t="n">
         <v>1.85</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR28" t="n">
         <v>2.18</v>
@@ -6013,7 +6013,7 @@
         <v>2.57</v>
       </c>
       <c r="AT28" t="n">
-        <v>3.42</v>
+        <v>2.85</v>
       </c>
       <c r="AU28" t="n">
         <v>3.08</v>
@@ -6025,7 +6025,7 @@
         <v>1.8</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AY28" t="n">
         <v>1.34</v>
@@ -6326,7 +6326,7 @@
         <v>3</v>
       </c>
       <c r="S30" t="n">
-        <v>3.04</v>
+        <v>2.62</v>
       </c>
       <c r="T30" t="n">
         <v>2.3</v>
@@ -6335,13 +6335,13 @@
         <v>3.81</v>
       </c>
       <c r="V30" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W30" t="n">
-        <v>2.76</v>
+        <v>3.12</v>
       </c>
       <c r="X30" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="Y30" t="n">
         <v>1.44</v>
@@ -6350,7 +6350,7 @@
         <v>6.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AB30" t="n">
         <v>1.02</v>
@@ -6359,10 +6359,10 @@
         <v>1.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.4</v>
+        <v>3.92</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AF30" t="n">
         <v>1.85</v>
@@ -6386,10 +6386,10 @@
         <v>2.1</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6398,46 +6398,46 @@
         <v>1.19</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AR30" t="n">
         <v>1.88</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AW30" t="n">
         <v>2.17</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AY30" t="n">
         <v>1.47</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="BA30" t="n">
         <v>2.55</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BC30" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.94</v>
+        <v>3.75</v>
       </c>
       <c r="BE30" t="n">
         <v>1.7</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.61</v>
+        <v>2.52</v>
       </c>
       <c r="Q33" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="X33" t="n">
         <v>3.42</v>
       </c>
-      <c r="R33" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U33" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W33" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.04</v>
-      </c>
       <c r="Y33" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AI33" t="n">
-        <v>7.2</v>
+        <v>8.1</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AN33" t="n">
-        <v>2.07</v>
+        <v>1.41</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.52</v>
+        <v>1.61</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.44</v>
+        <v>3.42</v>
       </c>
       <c r="R34" t="n">
-        <v>3.41</v>
+        <v>5.34</v>
       </c>
       <c r="S34" t="n">
-        <v>3.44</v>
+        <v>2.22</v>
       </c>
       <c r="T34" t="n">
-        <v>1.66</v>
+        <v>2.01</v>
       </c>
       <c r="U34" t="n">
-        <v>4.59</v>
+        <v>6.19</v>
       </c>
       <c r="V34" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W34" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="X34" t="n">
-        <v>3.42</v>
+        <v>3.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z34" t="n">
-        <v>8.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.44</v>
+        <v>2.74</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="AG34" t="n">
-        <v>4.2</v>
+        <v>3.74</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AI34" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.41</v>
+        <v>2.07</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="BD34" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -2392,7 +2392,7 @@
         <v>2.05</v>
       </c>
       <c r="U10" t="n">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="V10" t="n">
         <v>1.38</v>
@@ -2404,7 +2404,7 @@
         <v>2.75</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
         <v>7</v>
@@ -2416,7 +2416,7 @@
         <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AD10" t="n">
         <v>3.3</v>
@@ -2428,22 +2428,22 @@
         <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AH10" t="n">
         <v>1.27</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="AJ10" t="n">
         <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AM10" t="n">
         <v>1.3</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="BD10" t="n">
         <v>3.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="S12" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U12" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="X12" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z12" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AB12" t="n">
         <v>1.05</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.52</v>
+        <v>3.75</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AF12" t="n">
         <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.24</v>
+        <v>2.46</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.97</v>
+        <v>3.28</v>
       </c>
       <c r="AU12" t="n">
         <v>3.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.49</v>
+        <v>2.34</v>
       </c>
       <c r="BB12" t="n">
         <v>1.22</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="BE12" t="n">
         <v>1.73</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,130 +3165,130 @@
         </is>
       </c>
       <c r="P14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AL14" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE14" t="n">
+      <c r="AM14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE14" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.73</v>
       </c>
       <c r="BF14" t="n">
         <v>1.2</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>2.87</v>
+        <v>4.05</v>
       </c>
       <c r="S15" t="n">
-        <v>2.64</v>
+        <v>2.11</v>
       </c>
       <c r="T15" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="U15" t="n">
-        <v>3.65</v>
+        <v>4.58</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>3.16</v>
+        <v>3.78</v>
       </c>
       <c r="X15" t="n">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.55</v>
+        <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.82</v>
+        <v>5.1</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="AI15" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.65</v>
+        <v>2.16</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.07</v>
+        <v>1.86</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.7</v>
+        <v>2.31</v>
       </c>
       <c r="AU15" t="n">
         <v>3.9</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.71</v>
+        <v>2.85</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.1</v>
+        <v>2.79</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK16" t="n">
         <v>1.62</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="AL16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD16" t="n">
         <v>3.8</v>
       </c>
-      <c r="R16" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U16" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE16" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.34</v>
+        <v>4.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="S18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD18" t="n">
         <v>4.2</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AM18" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AN18" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4070,13 +4070,13 @@
         <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="BF18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.74</v>
+        <v>11.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="R19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.58</v>
       </c>
-      <c r="S19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T19" t="n">
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2.45</v>
       </c>
-      <c r="U19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AG19" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="AM19" t="n">
-        <v>2.1</v>
+        <v>1.08</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4267,13 +4267,13 @@
         <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="BF19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>11.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BB20" t="n">
         <v>1.22</v>
       </c>
-      <c r="S20" t="n">
-        <v>8</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>0</v>
-      </c>
       <c r="BC20" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.97</v>
+        <v>1.79</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>4.6</v>
+        <v>1.49</v>
       </c>
       <c r="T21" t="n">
-        <v>2.19</v>
+        <v>3.35</v>
       </c>
       <c r="U21" t="n">
-        <v>2.27</v>
+        <v>7.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.45</v>
+        <v>1.63</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="Z21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>3.65</v>
       </c>
       <c r="AG21" t="n">
-        <v>3</v>
+        <v>1.58</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.26</v>
+        <v>2.28</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AL21" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.2</v>
+        <v>3.65</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,35 +4741,35 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.49</v>
       </c>
-      <c r="T22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2</v>
-      </c>
       <c r="Z22" t="n">
         <v>0</v>
       </c>
@@ -4780,40 +4780,40 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.21</v>
+        <v>1.6</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.65</v>
+        <v>2.1</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.58</v>
+        <v>2.48</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.15</v>
+        <v>1.43</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.28</v>
+        <v>4.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.06</v>
+        <v>1.88</v>
       </c>
       <c r="AN22" t="n">
-        <v>3.65</v>
+        <v>1.15</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4858,16 +4858,16 @@
         <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5726,19 +5726,19 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="R27" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="S27" t="n">
         <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="U27" t="n">
         <v>5.75</v>
@@ -5765,28 +5765,28 @@
         <v>1</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.38</v>
+        <v>3.52</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AG27" t="n">
         <v>3.05</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AI27" t="n">
         <v>6.75</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK27" t="n">
         <v>1.95</v>
@@ -5795,10 +5795,10 @@
         <v>1.73</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5807,7 +5807,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AR27" t="n">
         <v>2.07</v>
@@ -5816,10 +5816,10 @@
         <v>2.12</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="AV27" t="n">
         <v>2.55</v>
@@ -5828,7 +5828,7 @@
         <v>1.97</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AY27" t="n">
         <v>1.38</v>
@@ -5837,10 +5837,10 @@
         <v>1.36</v>
       </c>
       <c r="BA27" t="n">
-        <v>3.85</v>
+        <v>3.76</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BC27" t="n">
         <v>2.04</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.91</v>
+        <v>3.4</v>
       </c>
       <c r="Q28" t="n">
         <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="S28" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="T28" t="n">
         <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="V28" t="n">
         <v>1.42</v>
       </c>
       <c r="W28" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="X28" t="n">
-        <v>2.9</v>
+        <v>3.21</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="AA28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB28" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AC28" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AE28" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.24</v>
+        <v>3.86</v>
       </c>
       <c r="AH28" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
         <v>1.26</v>
       </c>
-      <c r="AI28" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK28" t="n">
+      <c r="AQ28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW28" t="n">
         <v>1.83</v>
       </c>
-      <c r="AL28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AX28" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.9</v>
+        <v>1.89</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.4</v>
+        <v>1.91</v>
       </c>
       <c r="Q29" t="n">
         <v>3.25</v>
       </c>
       <c r="R29" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="S29" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="T29" t="n">
         <v>2.1</v>
       </c>
       <c r="U29" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="V29" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W29" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="X29" t="n">
-        <v>3.21</v>
+        <v>2.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AK29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL29" t="n">
         <v>1.85</v>
       </c>
-      <c r="AL29" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AM29" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="AW29" t="n">
         <v>1.8</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.89</v>
+        <v>2.9</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6529,19 +6529,19 @@
         <v>2.25</v>
       </c>
       <c r="U31" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="V31" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W31" t="n">
-        <v>3.07</v>
+        <v>2.73</v>
       </c>
       <c r="X31" t="n">
         <v>2.73</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z31" t="n">
         <v>6.4</v>
@@ -6550,25 +6550,25 @@
         <v>1.08</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AE31" t="n">
         <v>1.96</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG31" t="n">
         <v>3.05</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AI31" t="n">
         <v>6.15</v>
@@ -6577,13 +6577,13 @@
         <v>1.1</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AN31" t="n">
         <v>1.35</v>
@@ -6592,40 +6592,40 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.04</v>
+        <v>2.44</v>
       </c>
       <c r="AS31" t="n">
         <v>2.74</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AX31" t="n">
         <v>1.35</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AZ31" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="BB31" t="n">
         <v>1.25</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="R33" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="S33" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="T33" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="U33" t="n">
-        <v>4.59</v>
+        <v>4.72</v>
       </c>
       <c r="V33" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W33" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="X33" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z33" t="n">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="AE33" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
         <v>2.38</v>
       </c>
-      <c r="AF33" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BE33" t="n">
         <v>1.33</v>
       </c>
-      <c r="BC33" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>1.46</v>
-      </c>
       <c r="BF33" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="Q34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="X34" t="n">
         <v>3.42</v>
       </c>
-      <c r="R34" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U34" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W34" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.04</v>
-      </c>
       <c r="Y34" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z34" t="n">
-        <v>7.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.12</v>
+        <v>2.41</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AI34" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AN34" t="n">
-        <v>2.07</v>
+        <v>1.41</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="R35" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>2.21</v>
       </c>
       <c r="T35" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="U35" t="n">
-        <v>4.2</v>
+        <v>6.29</v>
       </c>
       <c r="V35" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W35" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="X35" t="n">
-        <v>3.65</v>
+        <v>3.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z35" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AA35" t="n">
         <v>1.03</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.21</v>
+        <v>2.74</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.78</v>
+        <v>2.18</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="AG35" t="n">
-        <v>5.6</v>
+        <v>3.74</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AI35" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="AJ35" t="n">
         <v>1.03</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.62</v>
+        <v>2.09</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="BC35" t="n">
-        <v>3</v>
+        <v>2.27</v>
       </c>
       <c r="BD35" t="n">
-        <v>2.5</v>
+        <v>3.28</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7702,25 +7702,25 @@
         <v>2.87</v>
       </c>
       <c r="R37" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="S37" t="n">
         <v>2.66</v>
       </c>
       <c r="T37" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="U37" t="n">
         <v>5.25</v>
       </c>
       <c r="V37" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="W37" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="X37" t="n">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="Y37" t="n">
         <v>1.19</v>
@@ -7732,28 +7732,28 @@
         <v>1.04</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AE37" t="n">
         <v>2.66</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AG37" t="n">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AI37" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AJ37" t="n">
         <v>1.03</v>
@@ -7765,10 +7765,10 @@
         <v>1.6</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
@@ -7783,22 +7783,22 @@
         <v>2.43</v>
       </c>
       <c r="AS37" t="n">
-        <v>3.57</v>
+        <v>3.42</v>
       </c>
       <c r="AT37" t="n">
         <v>5.41</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="AV37" t="n">
         <v>1.79</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AY37" t="n">
         <v>1.07</v>
@@ -7813,16 +7813,16 @@
         <v>1.44</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="BE37" t="n">
         <v>1.36</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7896,10 +7896,10 @@
         <v>1.45</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="S38" t="n">
         <v>1.95</v>
@@ -7911,7 +7911,7 @@
         <v>6</v>
       </c>
       <c r="V38" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W38" t="n">
         <v>3.05</v>
@@ -7923,7 +7923,7 @@
         <v>1.44</v>
       </c>
       <c r="Z38" t="n">
-        <v>6.1</v>
+        <v>6.15</v>
       </c>
       <c r="AA38" t="n">
         <v>1.06</v>
@@ -7938,22 +7938,22 @@
         <v>3.68</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AG38" t="n">
         <v>2.83</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AI38" t="n">
         <v>5</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK38" t="n">
         <v>1.85</v>
@@ -7974,31 +7974,31 @@
         <v>1.24</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AR38" t="n">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="AS38" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AV38" t="n">
         <v>2.38</v>
       </c>
-      <c r="AT38" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AW38" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AZ38" t="n">
         <v>1.34</v>
@@ -8007,13 +8007,13 @@
         <v>3.6</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BC38" t="n">
         <v>1.98</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BE38" t="n">
         <v>1.76</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,130 +2968,130 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.25</v>
+        <v>3.64</v>
       </c>
       <c r="R13" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="S13" t="n">
         <v>2.64</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.02</v>
-      </c>
       <c r="T13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA13" t="n">
         <v>2.1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.23</v>
       </c>
       <c r="BB13" t="n">
         <v>1.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BD13" t="n">
         <v>4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="BF13" t="n">
         <v>1.2</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,130 +3165,130 @@
         </is>
       </c>
       <c r="P14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.36</v>
-      </c>
       <c r="U14" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W14" t="n">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="X14" t="n">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="Z14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI14" t="n">
         <v>5.55</v>
       </c>
-      <c r="AA14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>5</v>
-      </c>
       <c r="AJ14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AR14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AX14" t="n">
         <v>1.67</v>
       </c>
-      <c r="AS14" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AY14" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="BB14" t="n">
         <v>1.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BD14" t="n">
         <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="BF14" t="n">
         <v>1.2</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.62</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="AL15" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD15" t="n">
         <v>3.8</v>
       </c>
-      <c r="R15" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U15" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE15" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="S16" t="n">
-        <v>2.55</v>
+        <v>2.11</v>
       </c>
       <c r="T16" t="n">
-        <v>2.06</v>
+        <v>2.47</v>
       </c>
       <c r="U16" t="n">
-        <v>3.5</v>
+        <v>4.58</v>
       </c>
       <c r="V16" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="W16" t="n">
-        <v>2.77</v>
+        <v>3.78</v>
       </c>
       <c r="X16" t="n">
-        <v>2.62</v>
+        <v>2.17</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="Z16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.52</v>
+        <v>5.1</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AF16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE16" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BF16" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.74</v>
+        <v>4.34</v>
       </c>
       <c r="Q18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD18" t="n">
         <v>4</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AM18" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4070,13 +4070,13 @@
         <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="BF18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>1.49</v>
       </c>
       <c r="T19" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="U19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.58</v>
       </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AH19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK19" t="n">
         <v>1.58</v>
       </c>
-      <c r="AI19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AL19" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4267,16 +4267,16 @@
         <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.8</v>
+        <v>11.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.72</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="T20" t="n">
-        <v>2.19</v>
+        <v>2.88</v>
       </c>
       <c r="U20" t="n">
-        <v>2.27</v>
+        <v>1.58</v>
       </c>
       <c r="V20" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF20" t="n">
         <v>2.45</v>
       </c>
-      <c r="Y20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE20" t="n">
+      <c r="AG20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL20" t="n">
         <v>1.75</v>
       </c>
-      <c r="AF20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2</v>
-      </c>
       <c r="AM20" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="BD20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S21" t="n">
-        <v>1.49</v>
+        <v>4.6</v>
       </c>
       <c r="T21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU21" t="n">
         <v>3.35</v>
       </c>
-      <c r="U21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.34</v>
+        <v>4.74</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="S22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD22" t="n">
         <v>4.2</v>
       </c>
-      <c r="T22" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>4</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AM22" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG22" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AN22" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4858,13 +4858,13 @@
         <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="BF22" t="n">
         <v>0</v>
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5532,10 +5532,10 @@
         <v>1.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>3.87</v>
+        <v>3.6</v>
       </c>
       <c r="S26" t="n">
         <v>2.25</v>
@@ -5553,7 +5553,7 @@
         <v>3.9</v>
       </c>
       <c r="X26" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Y26" t="n">
         <v>1.63</v>
@@ -5568,10 +5568,10 @@
         <v>1.02</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.95</v>
+        <v>5.25</v>
       </c>
       <c r="AE26" t="n">
         <v>1.43</v>
@@ -5583,7 +5583,7 @@
         <v>2.23</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AI26" t="n">
         <v>3.75</v>
@@ -5619,7 +5619,7 @@
         <v>1.84</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="AU26" t="n">
         <v>4.2</v>
@@ -5634,7 +5634,7 @@
         <v>1.84</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="AZ26" t="n">
         <v>1.4</v>
@@ -5643,7 +5643,7 @@
         <v>2.38</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BC26" t="n">
         <v>1.64</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.4</v>
+        <v>1.91</v>
       </c>
       <c r="Q28" t="n">
         <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="S28" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="T28" t="n">
         <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="V28" t="n">
         <v>1.42</v>
       </c>
       <c r="W28" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="X28" t="n">
-        <v>3.21</v>
+        <v>2.9</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY28" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z28" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AZ28" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.89</v>
+        <v>2.9</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.91</v>
+        <v>3.4</v>
       </c>
       <c r="Q29" t="n">
         <v>3.25</v>
       </c>
       <c r="R29" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="S29" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="T29" t="n">
         <v>2.1</v>
       </c>
       <c r="U29" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="V29" t="n">
         <v>1.42</v>
       </c>
       <c r="W29" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="X29" t="n">
-        <v>2.9</v>
+        <v>3.21</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB29" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB29" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AC29" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AE29" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.24</v>
+        <v>3.86</v>
       </c>
       <c r="AH29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
         <v>1.26</v>
       </c>
-      <c r="AI29" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK29" t="n">
+      <c r="AQ29" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW29" t="n">
         <v>1.83</v>
       </c>
-      <c r="AL29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AX29" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.9</v>
+        <v>1.89</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="R34" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="S34" t="n">
-        <v>3.46</v>
+        <v>2.21</v>
       </c>
       <c r="T34" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="U34" t="n">
-        <v>3.6</v>
+        <v>6.29</v>
       </c>
       <c r="V34" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="W34" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="X34" t="n">
-        <v>3.42</v>
+        <v>3.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z34" t="n">
-        <v>8.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.44</v>
+        <v>2.74</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.41</v>
+        <v>2.18</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AG34" t="n">
-        <v>4.2</v>
+        <v>3.74</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AI34" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.41</v>
+        <v>2.09</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="BD34" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R35" t="n">
+        <v>3</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U35" t="n">
         <v>3.6</v>
       </c>
-      <c r="R35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U35" t="n">
-        <v>6.29</v>
-      </c>
       <c r="V35" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="W35" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="X35" t="n">
-        <v>3.04</v>
+        <v>3.42</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z35" t="n">
-        <v>7.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.18</v>
+        <v>2.41</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AI35" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AN35" t="n">
-        <v>2.09</v>
+        <v>1.41</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.35</v>
+        <v>2.87</v>
       </c>
       <c r="R36" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="S36" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U36" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR36" t="n">
         <v>2.43</v>
       </c>
-      <c r="T36" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U36" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W36" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>0</v>
-      </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.87</v>
+        <v>3.35</v>
       </c>
       <c r="R37" t="n">
-        <v>4</v>
+        <v>4.01</v>
       </c>
       <c r="S37" t="n">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="T37" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="U37" t="n">
-        <v>5.25</v>
+        <v>4.35</v>
       </c>
       <c r="V37" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="W37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
         <v>2.2</v>
       </c>
-      <c r="X37" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>2.8</v>
-      </c>
       <c r="BD37" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="R13" t="n">
-        <v>2.87</v>
+        <v>4.05</v>
       </c>
       <c r="S13" t="n">
-        <v>2.64</v>
+        <v>2.11</v>
       </c>
       <c r="T13" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="U13" t="n">
-        <v>3.65</v>
+        <v>4.58</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>3.16</v>
+        <v>3.78</v>
       </c>
       <c r="X13" t="n">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.55</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.82</v>
+        <v>5.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="AI13" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.65</v>
+        <v>2.16</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.07</v>
+        <v>1.86</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.7</v>
+        <v>2.31</v>
       </c>
       <c r="AU13" t="n">
         <v>3.9</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.71</v>
+        <v>2.85</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.1</v>
+        <v>2.79</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="BD13" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,130 +3165,130 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.25</v>
+        <v>3.64</v>
       </c>
       <c r="R14" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="S14" t="n">
         <v>2.64</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.02</v>
-      </c>
       <c r="T14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA14" t="n">
         <v>2.1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.23</v>
       </c>
       <c r="BB14" t="n">
         <v>1.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BD14" t="n">
         <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="BF14" t="n">
         <v>1.2</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.06</v>
+        <v>2.37</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U15" t="n">
         <v>3</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.5</v>
-      </c>
       <c r="V15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.39</v>
       </c>
-      <c r="W15" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="AI15" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AY15" t="n">
         <v>1.43</v>
       </c>
-      <c r="Z15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF15" t="n">
+      <c r="AZ15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC15" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.98</v>
-      </c>
       <c r="BD15" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK16" t="n">
         <v>1.62</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="AL16" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD16" t="n">
         <v>3.8</v>
       </c>
-      <c r="R16" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U16" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE16" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.34</v>
+        <v>3.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="S18" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="U18" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X18" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AD18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BD18" t="n">
         <v>4</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
+      <c r="BE18" t="n">
         <v>1.79</v>
       </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.81</v>
-      </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,22 +4150,22 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S19" t="n">
-        <v>1.49</v>
+        <v>4.7</v>
       </c>
       <c r="T19" t="n">
-        <v>3.35</v>
+        <v>2.45</v>
       </c>
       <c r="U19" t="n">
-        <v>7.5</v>
+        <v>2.05</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4174,10 +4174,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -4189,40 +4189,40 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.21</v>
+        <v>1.55</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.65</v>
+        <v>2.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.28</v>
+        <v>4.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.06</v>
+        <v>2.1</v>
       </c>
       <c r="AN19" t="n">
-        <v>3.65</v>
+        <v>1.11</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4267,16 +4267,16 @@
         <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>1.49</v>
       </c>
       <c r="T20" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="U20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.58</v>
       </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AH20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.58</v>
       </c>
-      <c r="AI20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AL20" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,16 +4464,16 @@
         <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.8</v>
+        <v>4.34</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="S21" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="U21" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.43</v>
       </c>
-      <c r="Z21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AI21" t="n">
-        <v>5.26</v>
+        <v>4.3</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AL21" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.24</v>
+        <v>1.88</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
         <v>1.79</v>
       </c>
-      <c r="AS21" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.94</v>
-      </c>
       <c r="BD21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.74</v>
+        <v>11.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="R22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U22" t="n">
         <v>1.58</v>
       </c>
-      <c r="S22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T22" t="n">
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF22" t="n">
         <v>2.45</v>
       </c>
-      <c r="U22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AG22" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="AM22" t="n">
-        <v>2.1</v>
+        <v>1.08</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4858,13 +4858,13 @@
         <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="BF22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="R23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W23" t="n">
         <v>2.56</v>
       </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U23" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="V23" t="n">
+      <c r="X23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC23" t="n">
         <v>1.38</v>
       </c>
-      <c r="W23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.06</v>
       </c>
-      <c r="AC23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH23" t="n">
+      <c r="AK23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY23" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY23" t="n">
+      <c r="AZ23" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BB23" t="n">
         <v>1.29</v>
       </c>
-      <c r="AZ23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC23" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="S24" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="U24" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="V24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN24" t="n">
         <v>1.44</v>
       </c>
-      <c r="W24" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.49</v>
+        <v>2.24</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.42</v>
+        <v>3.06</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.09</v>
+        <v>3.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AY24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BB24" t="n">
         <v>1.25</v>
       </c>
-      <c r="AZ24" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC24" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BF25" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R26" t="n">
-        <v>3.6</v>
+        <v>8.5</v>
       </c>
       <c r="S26" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="T26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W26" t="n">
         <v>2.6</v>
       </c>
-      <c r="U26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W26" t="n">
+      <c r="X26" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BD26" t="n">
         <v>3.9</v>
       </c>
-      <c r="X26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AM26" t="n">
+      <c r="BE26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BF26" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>1.3</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.91</v>
+        <v>3.4</v>
       </c>
       <c r="Q28" t="n">
         <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="S28" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="T28" t="n">
         <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="V28" t="n">
         <v>1.42</v>
       </c>
       <c r="W28" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="X28" t="n">
-        <v>2.9</v>
+        <v>3.21</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="AA28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB28" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AC28" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AE28" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.24</v>
+        <v>3.86</v>
       </c>
       <c r="AH28" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
         <v>1.26</v>
       </c>
-      <c r="AI28" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK28" t="n">
+      <c r="AQ28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW28" t="n">
         <v>1.83</v>
       </c>
-      <c r="AL28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AX28" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.9</v>
+        <v>1.89</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.4</v>
+        <v>1.91</v>
       </c>
       <c r="Q29" t="n">
         <v>3.25</v>
       </c>
       <c r="R29" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="S29" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="T29" t="n">
         <v>2.1</v>
       </c>
       <c r="U29" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="V29" t="n">
         <v>1.42</v>
       </c>
       <c r="W29" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="X29" t="n">
-        <v>3.21</v>
+        <v>2.9</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY29" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z29" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AZ29" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.89</v>
+        <v>2.9</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="R33" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>2.21</v>
       </c>
       <c r="T33" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="U33" t="n">
-        <v>4.72</v>
+        <v>6.29</v>
       </c>
       <c r="V33" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W33" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="X33" t="n">
-        <v>3.65</v>
+        <v>3.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z33" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AA33" t="n">
         <v>1.03</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.17</v>
+        <v>2.74</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.78</v>
+        <v>2.18</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="AG33" t="n">
-        <v>5.6</v>
+        <v>3.74</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AI33" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="AJ33" t="n">
         <v>1.03</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.56</v>
+        <v>2.09</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.91</v>
+        <v>2.27</v>
       </c>
       <c r="BD33" t="n">
-        <v>2.62</v>
+        <v>3.28</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U34" t="n">
         <v>3.6</v>
       </c>
-      <c r="R34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U34" t="n">
-        <v>6.29</v>
-      </c>
       <c r="V34" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="W34" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="X34" t="n">
-        <v>3.04</v>
+        <v>3.42</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z34" t="n">
-        <v>7.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.18</v>
+        <v>2.41</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AI34" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AN34" t="n">
-        <v>2.09</v>
+        <v>1.41</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S35" t="n">
         <v>3</v>
       </c>
-      <c r="S35" t="n">
-        <v>3.46</v>
-      </c>
       <c r="T35" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="U35" t="n">
-        <v>3.6</v>
+        <v>4.72</v>
       </c>
       <c r="V35" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="W35" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="X35" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z35" t="n">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.41</v>
+        <v>2.78</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AG35" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AI35" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BE35" t="n">
         <v>1.33</v>
       </c>
-      <c r="BC35" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>1.46</v>
-      </c>
       <c r="BF35" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,46 +2771,46 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>3.1</v>
+        <v>2.64</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>3.02</v>
       </c>
       <c r="T12" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W12" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="X12" t="n">
-        <v>2.33</v>
+        <v>2.66</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.95</v>
+        <v>6.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AD12" t="n">
         <v>3.75</v>
@@ -2819,82 +2819,82 @@
         <v>1.8</v>
       </c>
       <c r="AF12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC12" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG12" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2</v>
-      </c>
       <c r="BD12" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="BF12" t="n">
         <v>1.2</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="R13" t="n">
-        <v>4.05</v>
+        <v>2.87</v>
       </c>
       <c r="S13" t="n">
-        <v>2.11</v>
+        <v>2.64</v>
       </c>
       <c r="T13" t="n">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="U13" t="n">
-        <v>4.58</v>
+        <v>3.65</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>3.78</v>
+        <v>3.16</v>
       </c>
       <c r="X13" t="n">
-        <v>2.17</v>
+        <v>2.55</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="Z13" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI13" t="n">
         <v>5</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AJ13" t="n">
         <v>1.12</v>
       </c>
-      <c r="AB13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AK13" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.16</v>
+        <v>1.65</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.86</v>
+        <v>2.07</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.31</v>
+        <v>2.7</v>
       </c>
       <c r="AU13" t="n">
         <v>3.9</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.79</v>
+        <v>2.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="R14" t="n">
-        <v>2.87</v>
+        <v>4.05</v>
       </c>
       <c r="S14" t="n">
-        <v>2.64</v>
+        <v>2.11</v>
       </c>
       <c r="T14" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="U14" t="n">
-        <v>3.65</v>
+        <v>4.58</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>3.16</v>
+        <v>3.78</v>
       </c>
       <c r="X14" t="n">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.55</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.82</v>
+        <v>5.1</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="AI14" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.65</v>
+        <v>2.16</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.07</v>
+        <v>1.86</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.7</v>
+        <v>2.31</v>
       </c>
       <c r="AU14" t="n">
         <v>3.9</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.71</v>
+        <v>2.85</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.1</v>
+        <v>2.79</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="BD14" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,46 +3362,46 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="S15" t="n">
-        <v>3.02</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="X15" t="n">
-        <v>2.66</v>
+        <v>2.33</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.4</v>
+        <v>5.95</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.05</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AC15" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AD15" t="n">
         <v>3.75</v>
@@ -3410,82 +3410,82 @@
         <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AI15" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.04</v>
+        <v>2.46</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.4</v>
+        <v>3.28</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.88</v>
+        <v>2.37</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="BF15" t="n">
         <v>1.2</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>4.6</v>
+        <v>1.49</v>
       </c>
       <c r="T18" t="n">
-        <v>2.19</v>
+        <v>3.35</v>
       </c>
       <c r="U18" t="n">
-        <v>2.27</v>
+        <v>7.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.45</v>
+        <v>1.63</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="Z18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>3.65</v>
       </c>
       <c r="AG18" t="n">
-        <v>3</v>
+        <v>1.58</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="AI18" t="n">
-        <v>5.26</v>
+        <v>2.28</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AL18" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.2</v>
+        <v>3.65</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.74</v>
+        <v>11.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="R19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.58</v>
       </c>
-      <c r="S19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T19" t="n">
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2.45</v>
       </c>
-      <c r="U19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AG19" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="AM19" t="n">
-        <v>2.1</v>
+        <v>1.08</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4267,13 +4267,13 @@
         <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="BF19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,22 +4347,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S20" t="n">
-        <v>1.49</v>
+        <v>4.7</v>
       </c>
       <c r="T20" t="n">
-        <v>3.35</v>
+        <v>2.45</v>
       </c>
       <c r="U20" t="n">
-        <v>7.5</v>
+        <v>2.05</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4371,10 +4371,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -4386,40 +4386,40 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.21</v>
+        <v>1.55</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.65</v>
+        <v>2.2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.28</v>
+        <v>4.1</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.06</v>
+        <v>2.1</v>
       </c>
       <c r="AN20" t="n">
-        <v>3.65</v>
+        <v>1.11</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,16 +4464,16 @@
         <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.34</v>
+        <v>3.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="T21" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="U21" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X21" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AD21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BD21" t="n">
         <v>4</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC21" t="n">
+      <c r="BE21" t="n">
         <v>1.79</v>
       </c>
-      <c r="BD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.81</v>
-      </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,22 +4741,22 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>11.2</v>
+        <v>4.34</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="U22" t="n">
-        <v>1.58</v>
+        <v>2.23</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4765,10 +4765,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -4780,40 +4780,40 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.08</v>
+        <v>1.88</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4858,13 +4858,13 @@
         <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="BF22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="R23" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="S23" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="U23" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="V23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN23" t="n">
         <v>1.44</v>
       </c>
-      <c r="W23" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.49</v>
+        <v>2.24</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.42</v>
+        <v>3.06</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.09</v>
+        <v>3.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AY23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BB23" t="n">
         <v>1.25</v>
       </c>
-      <c r="AZ23" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC23" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="R24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W24" t="n">
         <v>2.56</v>
       </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U24" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="V24" t="n">
+      <c r="X24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC24" t="n">
         <v>1.38</v>
       </c>
-      <c r="W24" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="AD24" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>1.06</v>
       </c>
-      <c r="AC24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH24" t="n">
+      <c r="AK24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY24" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY24" t="n">
+      <c r="AZ24" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BB24" t="n">
         <v>1.29</v>
       </c>
-      <c r="AZ24" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC24" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R25" t="n">
-        <v>3.6</v>
+        <v>8.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="T25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W25" t="n">
         <v>2.6</v>
       </c>
-      <c r="U25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W25" t="n">
+      <c r="X25" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BD25" t="n">
         <v>3.9</v>
       </c>
-      <c r="X25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AM25" t="n">
+      <c r="BE25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BF25" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.3</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BF26" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R26" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="V33" t="n">
         <v>1.55</v>
       </c>
-      <c r="Q33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U33" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.44</v>
-      </c>
       <c r="W33" t="n">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="X33" t="n">
-        <v>3.04</v>
+        <v>3.65</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AA33" t="n">
         <v>1.03</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.74</v>
+        <v>2.17</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.18</v>
+        <v>2.78</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.74</v>
+        <v>5.6</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AI33" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="AJ33" t="n">
         <v>1.03</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AN33" t="n">
-        <v>2.09</v>
+        <v>1.56</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.27</v>
+        <v>2.91</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.28</v>
+        <v>2.62</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="R35" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>2.21</v>
       </c>
       <c r="T35" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="U35" t="n">
-        <v>4.72</v>
+        <v>6.29</v>
       </c>
       <c r="V35" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W35" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="X35" t="n">
-        <v>3.65</v>
+        <v>3.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z35" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AA35" t="n">
         <v>1.03</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.17</v>
+        <v>2.74</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.78</v>
+        <v>2.18</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="AG35" t="n">
-        <v>5.6</v>
+        <v>3.74</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AI35" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="AJ35" t="n">
         <v>1.03</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.56</v>
+        <v>2.09</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.91</v>
+        <v>2.27</v>
       </c>
       <c r="BD35" t="n">
-        <v>2.62</v>
+        <v>3.28</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,130 +2771,130 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>3.64</v>
       </c>
       <c r="R12" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="S12" t="n">
         <v>2.64</v>
       </c>
-      <c r="S12" t="n">
-        <v>3.02</v>
-      </c>
       <c r="T12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA12" t="n">
         <v>2.1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>2.23</v>
       </c>
       <c r="BB12" t="n">
         <v>1.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BD12" t="n">
         <v>4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="BF12" t="n">
         <v>1.2</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="R13" t="n">
-        <v>2.87</v>
+        <v>4.05</v>
       </c>
       <c r="S13" t="n">
-        <v>2.64</v>
+        <v>2.11</v>
       </c>
       <c r="T13" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="U13" t="n">
-        <v>3.65</v>
+        <v>4.58</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>3.16</v>
+        <v>3.78</v>
       </c>
       <c r="X13" t="n">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.55</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.82</v>
+        <v>5.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="AI13" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.65</v>
+        <v>2.16</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.07</v>
+        <v>1.86</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.7</v>
+        <v>2.31</v>
       </c>
       <c r="AU13" t="n">
         <v>3.9</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.71</v>
+        <v>2.85</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.1</v>
+        <v>2.79</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="BD13" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.62</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="AL14" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD14" t="n">
         <v>3.8</v>
       </c>
-      <c r="R14" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U14" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE14" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>2.37</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U16" t="n">
         <v>3</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3.5</v>
-      </c>
       <c r="V16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.39</v>
       </c>
-      <c r="W16" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="AI16" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AY16" t="n">
         <v>1.43</v>
       </c>
-      <c r="Z16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF16" t="n">
+      <c r="AZ16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC16" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.98</v>
-      </c>
       <c r="BD16" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,22 +3953,22 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>1.49</v>
+        <v>8</v>
       </c>
       <c r="T18" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="U18" t="n">
-        <v>7.5</v>
+        <v>1.58</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3977,10 +3977,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3992,40 +3992,40 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.21</v>
+        <v>1.45</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.65</v>
+        <v>2.45</v>
       </c>
       <c r="AG18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.58</v>
       </c>
-      <c r="AH18" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AI18" t="n">
-        <v>2.28</v>
+        <v>3.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AN18" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4070,16 +4070,16 @@
         <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>11.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="R19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BB19" t="n">
         <v>1.22</v>
       </c>
-      <c r="S19" t="n">
-        <v>8</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>0</v>
-      </c>
       <c r="BC19" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.97</v>
+        <v>1.79</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>4.6</v>
+        <v>1.49</v>
       </c>
       <c r="T21" t="n">
-        <v>2.19</v>
+        <v>3.35</v>
       </c>
       <c r="U21" t="n">
-        <v>2.27</v>
+        <v>7.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.45</v>
+        <v>1.63</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="Z21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>3.65</v>
       </c>
       <c r="AG21" t="n">
-        <v>3</v>
+        <v>1.58</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.26</v>
+        <v>2.28</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AL21" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.2</v>
+        <v>3.65</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="R23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W23" t="n">
         <v>2.56</v>
       </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U23" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="V23" t="n">
+      <c r="X23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC23" t="n">
         <v>1.38</v>
       </c>
-      <c r="W23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.06</v>
       </c>
-      <c r="AC23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH23" t="n">
+      <c r="AK23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY23" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY23" t="n">
+      <c r="AZ23" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BB23" t="n">
         <v>1.29</v>
       </c>
-      <c r="AZ23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC23" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="S24" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="U24" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="V24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN24" t="n">
         <v>1.44</v>
       </c>
-      <c r="W24" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.49</v>
+        <v>2.24</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.42</v>
+        <v>3.06</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.09</v>
+        <v>3.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AY24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BB24" t="n">
         <v>1.25</v>
       </c>
-      <c r="AZ24" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC24" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.4</v>
+        <v>1.91</v>
       </c>
       <c r="Q28" t="n">
         <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="S28" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="T28" t="n">
         <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="V28" t="n">
         <v>1.42</v>
       </c>
       <c r="W28" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="X28" t="n">
-        <v>3.21</v>
+        <v>2.9</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY28" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z28" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AZ28" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.89</v>
+        <v>2.9</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.91</v>
+        <v>3.4</v>
       </c>
       <c r="Q29" t="n">
         <v>3.25</v>
       </c>
       <c r="R29" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="S29" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="T29" t="n">
         <v>2.1</v>
       </c>
       <c r="U29" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="V29" t="n">
         <v>1.42</v>
       </c>
       <c r="W29" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="X29" t="n">
-        <v>2.9</v>
+        <v>3.21</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB29" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB29" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AC29" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AE29" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.24</v>
+        <v>3.86</v>
       </c>
       <c r="AH29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
         <v>1.26</v>
       </c>
-      <c r="AI29" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK29" t="n">
+      <c r="AQ29" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW29" t="n">
         <v>1.83</v>
       </c>
-      <c r="AL29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AX29" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.9</v>
+        <v>1.89</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="R33" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>2.21</v>
       </c>
       <c r="T33" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="U33" t="n">
-        <v>4.72</v>
+        <v>6.29</v>
       </c>
       <c r="V33" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W33" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="X33" t="n">
-        <v>3.65</v>
+        <v>3.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z33" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AA33" t="n">
         <v>1.03</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.17</v>
+        <v>2.74</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.78</v>
+        <v>2.18</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="AG33" t="n">
-        <v>5.6</v>
+        <v>3.74</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AI33" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="AJ33" t="n">
         <v>1.03</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.56</v>
+        <v>2.09</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.91</v>
+        <v>2.27</v>
       </c>
       <c r="BD33" t="n">
-        <v>2.62</v>
+        <v>3.28</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="V35" t="n">
         <v>1.55</v>
       </c>
-      <c r="Q35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U35" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.44</v>
-      </c>
       <c r="W35" t="n">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="X35" t="n">
-        <v>3.04</v>
+        <v>3.65</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z35" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AA35" t="n">
         <v>1.03</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.74</v>
+        <v>2.17</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.18</v>
+        <v>2.78</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.74</v>
+        <v>5.6</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AI35" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="AJ35" t="n">
         <v>1.03</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AN35" t="n">
-        <v>2.09</v>
+        <v>1.56</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.27</v>
+        <v>2.91</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.28</v>
+        <v>2.62</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -1007,70 +1007,70 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -2455,40 +2455,40 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BB10" t="n">
         <v>1.21</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="R12" t="n">
-        <v>2.87</v>
+        <v>4.05</v>
       </c>
       <c r="S12" t="n">
-        <v>2.64</v>
+        <v>2.11</v>
       </c>
       <c r="T12" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="U12" t="n">
-        <v>3.65</v>
+        <v>4.58</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="W12" t="n">
-        <v>3.16</v>
+        <v>3.78</v>
       </c>
       <c r="X12" t="n">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.55</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.82</v>
+        <v>5.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="AI12" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.65</v>
+        <v>2.16</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.07</v>
+        <v>1.86</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.7</v>
+        <v>2.31</v>
       </c>
       <c r="AU12" t="n">
         <v>3.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.71</v>
+        <v>2.85</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.1</v>
+        <v>2.79</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="BD12" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.62</v>
+        <v>2.37</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="R13" t="n">
-        <v>4.05</v>
+        <v>2.64</v>
       </c>
       <c r="S13" t="n">
-        <v>2.11</v>
+        <v>3.02</v>
       </c>
       <c r="T13" t="n">
-        <v>2.47</v>
+        <v>2.1</v>
       </c>
       <c r="U13" t="n">
-        <v>4.58</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="W13" t="n">
-        <v>3.78</v>
+        <v>2.95</v>
       </c>
       <c r="X13" t="n">
-        <v>2.17</v>
+        <v>2.66</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AD13" t="n">
-        <v>5.1</v>
+        <v>3.75</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.25</v>
+        <v>2.92</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="AI13" t="n">
-        <v>3.8</v>
+        <v>5.55</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.16</v>
+        <v>1.49</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3049,52 +3049,52 @@
         <v>1.21</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.9</v>
+        <v>3.77</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.79</v>
+        <v>2.23</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BC13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE13" t="n">
         <v>1.75</v>
       </c>
-      <c r="BD13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.95</v>
-      </c>
       <c r="BF13" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="X14" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z14" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.44</v>
+        <v>3.75</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
         <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AJ14" t="n">
         <v>1.1</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="AM14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
         <v>1.26</v>
       </c>
-      <c r="AN14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
+      <c r="AQ14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BB14" t="n">
         <v>1.22</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.19</v>
-      </c>
       <c r="BC14" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U15" t="n">
         <v>3.5</v>
       </c>
-      <c r="R15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.4</v>
-      </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W15" t="n">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="X15" t="n">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AF15" t="n">
         <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AJ15" t="n">
         <v>1.1</v>
       </c>
       <c r="AK15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN15" t="n">
         <v>1.67</v>
       </c>
-      <c r="AL15" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.23</v>
+        <v>1.84</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.46</v>
+        <v>2.31</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.34</v>
+        <v>2.49</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BC15" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,130 +3559,130 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.25</v>
+        <v>3.64</v>
       </c>
       <c r="R16" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="S16" t="n">
         <v>2.64</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.02</v>
-      </c>
       <c r="T16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA16" t="n">
         <v>2.1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>2.23</v>
       </c>
       <c r="BB16" t="n">
         <v>1.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BD16" t="n">
         <v>4</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="BF16" t="n">
         <v>1.2</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,22 +3953,22 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>11.2</v>
+        <v>4.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="U18" t="n">
-        <v>1.58</v>
+        <v>2.23</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3977,10 +3977,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3992,40 +3992,40 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.08</v>
+        <v>1.88</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4070,13 +4070,13 @@
         <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="BF18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.8</v>
+        <v>11.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.72</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="T19" t="n">
-        <v>2.19</v>
+        <v>2.88</v>
       </c>
       <c r="U19" t="n">
-        <v>2.27</v>
+        <v>1.58</v>
       </c>
       <c r="V19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2.45</v>
       </c>
-      <c r="Y19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE19" t="n">
+      <c r="AG19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL19" t="n">
         <v>1.75</v>
       </c>
-      <c r="AF19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2</v>
-      </c>
       <c r="AM19" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="BD19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.58</v>
       </c>
-      <c r="S20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
+      <c r="AH20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL20" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AM20" t="n">
-        <v>2.1</v>
+        <v>1.06</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.11</v>
+        <v>3.65</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,16 +4464,16 @@
         <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S21" t="n">
-        <v>1.49</v>
+        <v>4.6</v>
       </c>
       <c r="T21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU21" t="n">
         <v>3.35</v>
       </c>
-      <c r="U21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.34</v>
+        <v>4.74</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="S22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD22" t="n">
         <v>4.2</v>
       </c>
-      <c r="T22" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>4</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AM22" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG22" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AN22" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4858,13 +4858,13 @@
         <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="BF22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="R23" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="S23" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="U23" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="V23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN23" t="n">
         <v>1.44</v>
       </c>
-      <c r="W23" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.49</v>
+        <v>2.24</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.42</v>
+        <v>3.06</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.09</v>
+        <v>3.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AY23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BB23" t="n">
         <v>1.25</v>
       </c>
-      <c r="AZ23" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC23" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="R24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W24" t="n">
         <v>2.56</v>
       </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U24" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="V24" t="n">
+      <c r="X24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC24" t="n">
         <v>1.38</v>
       </c>
-      <c r="W24" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="AD24" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>1.06</v>
       </c>
-      <c r="AC24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH24" t="n">
+      <c r="AK24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY24" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY24" t="n">
+      <c r="AZ24" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BB24" t="n">
         <v>1.29</v>
       </c>
-      <c r="AZ24" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC24" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BF25" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R26" t="n">
-        <v>3.6</v>
+        <v>8.5</v>
       </c>
       <c r="S26" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="T26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W26" t="n">
         <v>2.6</v>
       </c>
-      <c r="U26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W26" t="n">
+      <c r="X26" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BD26" t="n">
         <v>3.9</v>
       </c>
-      <c r="X26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AM26" t="n">
+      <c r="BE26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BF26" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>1.3</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S34" t="n">
         <v>3</v>
       </c>
-      <c r="S34" t="n">
-        <v>3.46</v>
-      </c>
       <c r="T34" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="U34" t="n">
-        <v>3.6</v>
+        <v>4.72</v>
       </c>
       <c r="V34" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="W34" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="X34" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z34" t="n">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.41</v>
+        <v>2.78</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AG34" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AI34" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BE34" t="n">
         <v>1.33</v>
       </c>
-      <c r="BC34" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>1.46</v>
-      </c>
       <c r="BF34" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R35" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>3.46</v>
       </c>
       <c r="T35" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="U35" t="n">
-        <v>4.72</v>
+        <v>3.6</v>
       </c>
       <c r="V35" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="W35" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="X35" t="n">
-        <v>3.65</v>
+        <v>3.42</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z35" t="n">
-        <v>13</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.17</v>
+        <v>2.44</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.78</v>
+        <v>2.41</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AG35" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AI35" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.91</v>
+        <v>2.41</v>
       </c>
       <c r="BD35" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK12" t="n">
         <v>1.62</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="AL12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD12" t="n">
         <v>3.8</v>
       </c>
-      <c r="R12" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W12" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE12" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.37</v>
+        <v>1.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="R13" t="n">
-        <v>2.64</v>
+        <v>4.05</v>
       </c>
       <c r="S13" t="n">
-        <v>3.02</v>
+        <v>2.11</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>4.58</v>
       </c>
       <c r="V13" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>2.95</v>
+        <v>3.78</v>
       </c>
       <c r="X13" t="n">
-        <v>2.66</v>
+        <v>2.17</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.93</v>
+        <v>2.35</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.92</v>
+        <v>2.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AI13" t="n">
-        <v>5.55</v>
+        <v>3.8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.49</v>
+        <v>2.16</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3049,52 +3049,52 @@
         <v>1.21</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.77</v>
+        <v>3.9</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.23</v>
+        <v>2.79</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BC13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE13" t="n">
         <v>1.95</v>
       </c>
-      <c r="BD13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BF13" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.06</v>
+        <v>2.37</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U15" t="n">
         <v>3</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.5</v>
-      </c>
       <c r="V15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.39</v>
       </c>
-      <c r="W15" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="AI15" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AY15" t="n">
         <v>1.43</v>
       </c>
-      <c r="Z15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF15" t="n">
+      <c r="AZ15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC15" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.98</v>
-      </c>
       <c r="BD15" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>11.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="R19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BB19" t="n">
         <v>1.22</v>
       </c>
-      <c r="S19" t="n">
-        <v>8</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>0</v>
-      </c>
       <c r="BC19" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.97</v>
+        <v>1.79</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,22 +4347,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S20" t="n">
-        <v>1.49</v>
+        <v>4.7</v>
       </c>
       <c r="T20" t="n">
-        <v>3.35</v>
+        <v>2.45</v>
       </c>
       <c r="U20" t="n">
-        <v>7.5</v>
+        <v>2.05</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4371,10 +4371,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -4386,40 +4386,40 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.21</v>
+        <v>1.55</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.65</v>
+        <v>2.2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.28</v>
+        <v>4.1</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.06</v>
+        <v>2.1</v>
       </c>
       <c r="AN20" t="n">
-        <v>3.65</v>
+        <v>1.11</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,16 +4464,16 @@
         <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.8</v>
+        <v>11.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.72</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.19</v>
+        <v>2.88</v>
       </c>
       <c r="U21" t="n">
-        <v>2.27</v>
+        <v>1.58</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF21" t="n">
         <v>2.45</v>
       </c>
-      <c r="Y21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE21" t="n">
+      <c r="AG21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL21" t="n">
         <v>1.75</v>
       </c>
-      <c r="AF21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2</v>
-      </c>
       <c r="AM21" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="BD21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.58</v>
       </c>
-      <c r="S22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
+      <c r="AH22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL22" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AM22" t="n">
-        <v>2.1</v>
+        <v>1.06</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.11</v>
+        <v>3.65</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4858,16 +4858,16 @@
         <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="R23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W23" t="n">
         <v>2.56</v>
       </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U23" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="V23" t="n">
+      <c r="X23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC23" t="n">
         <v>1.38</v>
       </c>
-      <c r="W23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.06</v>
       </c>
-      <c r="AC23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH23" t="n">
+      <c r="AK23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY23" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY23" t="n">
+      <c r="AZ23" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BB23" t="n">
         <v>1.29</v>
       </c>
-      <c r="AZ23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC23" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="S24" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="U24" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="V24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN24" t="n">
         <v>1.44</v>
       </c>
-      <c r="W24" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.49</v>
+        <v>2.24</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.42</v>
+        <v>3.06</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.09</v>
+        <v>3.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AY24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BB24" t="n">
         <v>1.25</v>
       </c>
-      <c r="AZ24" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC24" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R25" t="n">
-        <v>3.6</v>
+        <v>8.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="T25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W25" t="n">
         <v>2.6</v>
       </c>
-      <c r="U25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W25" t="n">
+      <c r="X25" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BD25" t="n">
         <v>3.9</v>
       </c>
-      <c r="X25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AM25" t="n">
+      <c r="BE25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BF25" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.3</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BF26" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R26" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.91</v>
+        <v>3.4</v>
       </c>
       <c r="Q28" t="n">
         <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="S28" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="T28" t="n">
         <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="V28" t="n">
         <v>1.42</v>
       </c>
       <c r="W28" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="X28" t="n">
-        <v>2.9</v>
+        <v>3.21</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="AA28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB28" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AC28" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AE28" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.24</v>
+        <v>3.86</v>
       </c>
       <c r="AH28" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
         <v>1.26</v>
       </c>
-      <c r="AI28" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK28" t="n">
+      <c r="AQ28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW28" t="n">
         <v>1.83</v>
       </c>
-      <c r="AL28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AX28" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.9</v>
+        <v>1.89</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.4</v>
+        <v>1.91</v>
       </c>
       <c r="Q29" t="n">
         <v>3.25</v>
       </c>
       <c r="R29" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="S29" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="T29" t="n">
         <v>2.1</v>
       </c>
       <c r="U29" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="V29" t="n">
         <v>1.42</v>
       </c>
       <c r="W29" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="X29" t="n">
-        <v>3.21</v>
+        <v>2.9</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY29" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z29" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AZ29" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.89</v>
+        <v>2.9</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.87</v>
+        <v>3.35</v>
       </c>
       <c r="R36" t="n">
-        <v>4</v>
+        <v>4.01</v>
       </c>
       <c r="S36" t="n">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="T36" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="U36" t="n">
-        <v>5.25</v>
+        <v>4.35</v>
       </c>
       <c r="V36" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="W36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
         <v>2.2</v>
       </c>
-      <c r="X36" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>2.8</v>
-      </c>
       <c r="BD36" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.35</v>
+        <v>2.87</v>
       </c>
       <c r="R37" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="S37" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U37" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X37" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR37" t="n">
         <v>2.43</v>
       </c>
-      <c r="T37" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U37" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W37" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>0</v>
-      </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>

--- a/jogos_2026-04-20.xlsx
+++ b/jogos_2026-04-20.xlsx
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.06</v>
+        <v>2.37</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U12" t="n">
         <v>3</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3.5</v>
-      </c>
       <c r="V12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.39</v>
       </c>
-      <c r="W12" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y12" t="n">
+      <c r="AI12" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AY12" t="n">
         <v>1.43</v>
       </c>
-      <c r="Z12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF12" t="n">
+      <c r="AZ12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC12" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.98</v>
-      </c>
       <c r="BD12" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD13" t="n">
         <v>4.05</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="V13" t="n">
+      <c r="BE13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BF13" t="n">
         <v>1.2</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.27</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R14" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="T14" t="n">
-        <v>2.12</v>
+        <v>2.47</v>
       </c>
       <c r="U14" t="n">
-        <v>3.4</v>
+        <v>4.58</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>3.2</v>
+        <v>3.78</v>
       </c>
       <c r="X14" t="n">
-        <v>2.33</v>
+        <v>2.17</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.95</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AF14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE14" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG14" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BF14" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.37</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="R15" t="n">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="S15" t="n">
-        <v>3.02</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="V15" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W15" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT15" t="n">
         <v>2.95</v>
       </c>
-      <c r="X15" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AU15" t="n">
-        <v>3.77</v>
+        <v>3.1</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.23</v>
+        <v>2.49</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.34</v>
+        <v>3.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="S18" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="U18" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X18" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AD18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BD18" t="n">
         <v>4</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
+      <c r="BE18" t="n">
         <v>1.79</v>
       </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.81</v>
-      </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.8</v>
+        <v>4.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="S19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T19" t="n">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="U19" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="V19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="Z19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN19" t="n">
         <v>1.11</v>
       </c>
-      <c r="AB19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="BD19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.74</v>
+        <v>11.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="R20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S20" t="n">
+        <v>8</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U20" t="n">
         <v>1.58</v>
       </c>
-      <c r="S20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T20" t="n">
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF20" t="n">
         <v>2.45</v>
       </c>
-      <c r="U20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AG20" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AI20" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="AM20" t="n">
-        <v>2.1</v>
+        <v>1.08</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,13 +4464,13 @@
         <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="BF20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,22 +4544,22 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>11.2</v>
+        <v>4.34</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="U21" t="n">
-        <v>1.58</v>
+        <v>2.23</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4568,10 +4568,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -4583,40 +4583,40 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AI21" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.08</v>
+        <v>1.88</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4661,13 +4661,13 @@
         <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="BD21" t="n">
         <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="BF21" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BF25" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R26" t="n">
-        <v>3.6</v>
+        <v>8.5</v>
       </c>
       <c r="S26" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="T26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W26" t="n">
         <v>2.6</v>
       </c>
-      <c r="U26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W26" t="n">
+      <c r="X26" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BD26" t="n">
         <v>3.9</v>
       </c>
-      <c r="X26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AM26" t="n">
+      <c r="BE26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BF26" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>1.3</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U33" t="n">
         <v>3.6</v>
       </c>
-      <c r="R33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U33" t="n">
-        <v>6.29</v>
-      </c>
       <c r="V33" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="W33" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="X33" t="n">
-        <v>3.04</v>
+        <v>3.42</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.18</v>
+        <v>2.41</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AI33" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AN33" t="n">
-        <v>2.09</v>
+        <v>1.41</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="R34" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>2.21</v>
       </c>
       <c r="T34" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="U34" t="n">
-        <v>4.72</v>
+        <v>6.29</v>
       </c>
       <c r="V34" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W34" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="X34" t="n">
-        <v>3.65</v>
+        <v>3.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z34" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AA34" t="n">
         <v>1.03</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.17</v>
+        <v>2.74</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.78</v>
+        <v>2.18</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="AG34" t="n">
-        <v>5.6</v>
+        <v>3.74</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AI34" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="AJ34" t="n">
         <v>1.03</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.56</v>
+        <v>2.09</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.91</v>
+        <v>2.27</v>
       </c>
       <c r="BD34" t="n">
-        <v>2.62</v>
+        <v>3.28</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S35" t="n">
         <v>3</v>
       </c>
-      <c r="S35" t="n">
-        <v>3.46</v>
-      </c>
       <c r="T35" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="U35" t="n">
-        <v>3.6</v>
+        <v>4.72</v>
       </c>
       <c r="V35" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="W35" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="X35" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z35" t="n">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.41</v>
+        <v>2.78</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AG35" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AI35" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BE35" t="n">
         <v>1.33</v>
       </c>
-      <c r="BC35" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>1.46</v>
-      </c>
       <c r="BF35" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.35</v>
+        <v>2.87</v>
       </c>
       <c r="R36" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="S36" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U36" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR36" t="n">
         <v>2.43</v>
       </c>
-      <c r="T36" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U36" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W36" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>0</v>
-      </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.87</v>
+        <v>3.35</v>
       </c>
       <c r="R37" t="n">
-        <v>4</v>
+        <v>4.01</v>
       </c>
       <c r="S37" t="n">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="T37" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="U37" t="n">
-        <v>5.25</v>
+        <v>4.35</v>
       </c>
       <c r="V37" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="W37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
         <v>2.2</v>
       </c>
-      <c r="X37" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>2.8</v>
-      </c>
       <c r="BD37" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        